--- a/public/Export/Exportar_Copiapo_Puerto.xlsx
+++ b/public/Export/Exportar_Copiapo_Puerto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B29702B-A91E-6040-B95E-0537F960E10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B78F841A-36CE-E540-B691-2CF46867F54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="845" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="845" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Utilidad!$J$38:$K$69</definedName>
@@ -190,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="122">
   <si>
     <t>Concentraducto CNN</t>
   </si>
@@ -535,6 +536,27 @@
   </si>
   <si>
     <t>Pellet Feed PM</t>
+  </si>
+  <si>
+    <t>PM Embar.</t>
+  </si>
+  <si>
+    <t>CNN Embar.</t>
+  </si>
+  <si>
+    <t>INVENTARIOS PUERTO PUNTA TOTORALILLO</t>
+  </si>
+  <si>
+    <t>PM Filtrado</t>
+  </si>
+  <si>
+    <t>CNN filtrado</t>
+  </si>
+  <si>
+    <t>Piscina CNN (tbn)</t>
+  </si>
+  <si>
+    <t>Piscina MAG (tbn)</t>
   </si>
 </sst>
 </file>
@@ -925,7 +947,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1549,43 +1571,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1616,6 +1605,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1905,9 +1905,6 @@
     <xf numFmtId="167" fontId="34" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2002,370 +1999,373 @@
     <xf numFmtId="164" fontId="34" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="52" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="50" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="40" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="52" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="13" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="13" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="13" borderId="45" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="48" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="34" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="35" fillId="13" borderId="53" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="40" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="13" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="48" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="13" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="13" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="13" borderId="45" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="54" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5710,6 +5710,52 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Utilidad"/>
+      <sheetName val="Datos Extra"/>
+      <sheetName val="Flujos"/>
+      <sheetName val="Diag Proceso Balance"/>
+      <sheetName val="Hoja1"/>
+      <sheetName val="Report"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="66">
+          <cell r="J66">
+            <v>2778</v>
+          </cell>
+          <cell r="K66">
+            <v>0.65663628509999994</v>
+          </cell>
+          <cell r="L66">
+            <v>1824.1356000077999</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="K67">
+            <v>0</v>
+          </cell>
+          <cell r="L67">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -6025,16 +6071,16 @@
   <sheetData>
     <row r="1" spans="1:54" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="76">
-        <v>179498</v>
+        <v>339786</v>
       </c>
       <c r="B1" s="76">
-        <v>179498</v>
+        <v>339674.47768000001</v>
       </c>
       <c r="C1" s="77">
-        <v>66.05</v>
+        <v>66.14</v>
       </c>
       <c r="D1" s="77">
-        <v>65.689928816999995</v>
+        <v>65.746340794999995</v>
       </c>
       <c r="E1" s="80">
         <v>0</v>
@@ -6052,16 +6098,16 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" s="78">
-        <v>-1732</v>
+        <v>3774</v>
       </c>
       <c r="B2" s="78">
-        <v>-1732</v>
+        <v>3774.0453121999999</v>
       </c>
       <c r="C2" s="79">
         <v>65.52</v>
       </c>
       <c r="D2" s="79">
-        <v>65.514753307999996</v>
+        <v>65.522263839000004</v>
       </c>
       <c r="E2" s="80">
         <v>0</v>
@@ -6116,16 +6162,16 @@
     </row>
     <row r="3" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="78">
-        <v>181230</v>
+        <v>336012</v>
       </c>
       <c r="B3" s="78">
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="C3" s="79">
         <v>65.52</v>
       </c>
       <c r="D3" s="79">
-        <v>65.688254678999996</v>
+        <v>65.748858436999996</v>
       </c>
       <c r="E3" s="80">
         <v>0</v>
@@ -6244,16 +6290,16 @@
     </row>
     <row r="5" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="78">
-        <v>181230</v>
+        <v>336012</v>
       </c>
       <c r="B5" s="78">
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="C5" s="79">
         <v>65.52</v>
       </c>
       <c r="D5" s="79">
-        <v>65.688254678999996</v>
+        <v>65.748858436999996</v>
       </c>
       <c r="E5" s="80">
         <v>0</v>
@@ -6308,16 +6354,16 @@
     </row>
     <row r="6" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="78">
-        <v>1906</v>
+        <v>1664</v>
       </c>
       <c r="B6" s="78">
-        <v>1906</v>
+        <v>1664.0298194</v>
       </c>
       <c r="C6" s="79">
         <v>65.52</v>
       </c>
       <c r="D6" s="79">
-        <v>65.524048007000005</v>
+        <v>65.519564517000006</v>
       </c>
       <c r="E6" s="80">
         <v>0</v>
@@ -6372,16 +6418,16 @@
     </row>
     <row r="7" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="78">
-        <v>177417</v>
+        <v>332684</v>
       </c>
       <c r="B7" s="78">
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="C7" s="79">
-        <v>66.400000000000006</v>
+        <v>66.08</v>
       </c>
       <c r="D7" s="79">
-        <v>65.69</v>
+        <v>65.75</v>
       </c>
       <c r="E7" s="80">
         <v>0</v>
@@ -6500,16 +6546,16 @@
     </row>
     <row r="9" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="78">
-        <v>179324</v>
+        <v>334348</v>
       </c>
       <c r="B9" s="78">
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="C9" s="79">
-        <v>65.69</v>
+        <v>65.75</v>
       </c>
       <c r="D9" s="79">
-        <v>65.69</v>
+        <v>65.75</v>
       </c>
       <c r="E9" s="80">
         <v>0</v>
@@ -6692,16 +6738,16 @@
     </row>
     <row r="12" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="81">
-        <v>13055</v>
+        <v>105341</v>
       </c>
       <c r="B12" s="81">
-        <v>13056</v>
+        <v>105229.40255</v>
       </c>
       <c r="C12" s="79">
-        <v>65.64</v>
+        <v>65.73</v>
       </c>
       <c r="D12" s="79">
-        <v>66.326749387000007</v>
+        <v>65.793525287999998</v>
       </c>
       <c r="E12" s="80">
         <v>0</v>
@@ -6756,16 +6802,16 @@
     </row>
     <row r="13" spans="1:54" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="82">
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="B13" s="82">
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="C13" s="83">
-        <v>65.64</v>
+        <v>65.73</v>
       </c>
       <c r="D13" s="83">
-        <v>65.64</v>
+        <v>65.73</v>
       </c>
       <c r="E13" s="80">
         <v>0</v>
@@ -6823,13 +6869,13 @@
         <v>49366</v>
       </c>
       <c r="B14" s="76">
-        <v>49366</v>
+        <v>49365.992154</v>
       </c>
       <c r="C14" s="77">
         <v>66.53</v>
       </c>
       <c r="D14" s="77">
-        <v>66.156524052999998</v>
+        <v>66.157444671999997</v>
       </c>
       <c r="E14" s="80">
         <v>0</v>
@@ -6887,13 +6933,13 @@
         <v>-2483</v>
       </c>
       <c r="B15" s="78">
-        <v>-2483</v>
+        <v>-2483.0078454999998</v>
       </c>
       <c r="C15" s="79">
         <v>65.77</v>
       </c>
       <c r="D15" s="79">
-        <v>65.752721887999996</v>
+        <v>65.749415862000006</v>
       </c>
       <c r="E15" s="80">
         <v>0</v>
@@ -6957,7 +7003,7 @@
         <v>65.77</v>
       </c>
       <c r="D16" s="79">
-        <v>66.137186345999993</v>
+        <v>66.137904487</v>
       </c>
       <c r="E16" s="80">
         <v>0</v>
@@ -7012,16 +7058,16 @@
     </row>
     <row r="17" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="78">
-        <v>-7700</v>
+        <v>-7836</v>
       </c>
       <c r="B17" s="78">
-        <v>-7699.9115773000003</v>
+        <v>-7833.7575975</v>
       </c>
       <c r="C17" s="79">
         <v>65.77</v>
       </c>
       <c r="D17" s="79">
-        <v>65.766740619000004</v>
+        <v>65.768112607999996</v>
       </c>
       <c r="E17" s="80">
         <v>0</v>
@@ -7044,16 +7090,16 @@
     </row>
     <row r="18" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="78">
-        <v>59549</v>
+        <v>59685</v>
       </c>
       <c r="B18" s="78">
-        <v>59548.911576999999</v>
+        <v>59682.757597999997</v>
       </c>
       <c r="C18" s="79">
         <v>65.77</v>
       </c>
       <c r="D18" s="79">
-        <v>66.089286233999999</v>
+        <v>66.089366851999998</v>
       </c>
       <c r="E18" s="80">
         <v>0</v>
@@ -7079,13 +7125,13 @@
         <v>-1846</v>
       </c>
       <c r="B19" s="78">
-        <v>-1846.0884226999999</v>
+        <v>-1845.9260609</v>
       </c>
       <c r="C19" s="79">
         <v>65.77</v>
       </c>
       <c r="D19" s="79">
-        <v>65.78045582</v>
+        <v>65.777149403999999</v>
       </c>
       <c r="E19" s="80">
         <v>0</v>
@@ -7109,10 +7155,10 @@
     </row>
     <row r="20" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="78">
-        <v>61395</v>
+        <v>61531</v>
       </c>
       <c r="B20" s="78">
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="C20" s="79">
         <v>65.77</v>
@@ -7179,10 +7225,10 @@
     </row>
     <row r="22" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="78">
-        <v>61395</v>
+        <v>61531</v>
       </c>
       <c r="B22" s="78">
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="C22" s="79">
         <v>65.77</v>
@@ -7252,7 +7298,7 @@
         <v>61395</v>
       </c>
       <c r="B24" s="78">
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="C24" s="79">
         <v>66.08</v>
@@ -7319,16 +7365,16 @@
     </row>
     <row r="26" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="81">
-        <v>11739</v>
+        <v>-228232</v>
       </c>
       <c r="B26" s="81">
-        <v>11739</v>
+        <v>-228098.31633999999</v>
       </c>
       <c r="C26" s="79">
         <v>66.08</v>
       </c>
       <c r="D26" s="79">
-        <v>67.941201124000003</v>
+        <v>65.660983711</v>
       </c>
       <c r="E26" s="80">
         <v>0</v>
@@ -7354,16 +7400,16 @@
     </row>
     <row r="27" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="82">
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="B27" s="82">
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="C27" s="83">
-        <v>65.64</v>
+        <v>65.75</v>
       </c>
       <c r="D27" s="83">
-        <v>65.64</v>
+        <v>65.75</v>
       </c>
       <c r="E27" s="80">
         <v>0</v>
@@ -7389,16 +7435,16 @@
     </row>
     <row r="28" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="78">
-        <v>-2778</v>
+        <v>-46714</v>
       </c>
       <c r="B28" s="78">
-        <v>-2778</v>
+        <v>-46714</v>
       </c>
       <c r="C28" s="79">
-        <v>65.64</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="D28" s="79">
-        <v>65.663628509999995</v>
+        <v>65.727023161999995</v>
       </c>
       <c r="E28" s="80">
         <v>0</v>
@@ -7424,16 +7470,16 @@
     </row>
     <row r="29" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="78">
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="B29" s="78">
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="C29" s="79">
-        <v>65.64</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="D29" s="79">
-        <v>65.663628509999995</v>
+        <v>65.727023161999995</v>
       </c>
       <c r="E29" s="80">
         <v>0</v>
@@ -7494,16 +7540,16 @@
     </row>
     <row r="31" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="78">
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="B31" s="78">
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="C31" s="79">
-        <v>65.64</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="D31" s="79">
-        <v>65.663628509999995</v>
+        <v>65.727023161999995</v>
       </c>
       <c r="E31" s="80">
         <v>0</v>
@@ -7529,16 +7575,16 @@
     </row>
     <row r="32" spans="1:32" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="84">
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="B32" s="84">
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="C32" s="79">
-        <v>65.64</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="D32" s="79">
-        <v>65.64</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="E32" s="80">
         <v>0</v>
@@ -7637,21 +7683,21 @@
       <c r="D36" s="80"/>
       <c r="E36" s="80"/>
       <c r="F36" s="87"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="185"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="182"/>
       <c r="I36" s="80"/>
-      <c r="J36" s="181" t="s">
+      <c r="J36" s="178" t="s">
         <v>19</v>
       </c>
-      <c r="K36" s="181"/>
-      <c r="L36" s="181"/>
+      <c r="K36" s="178"/>
+      <c r="L36" s="178"/>
       <c r="M36" s="80"/>
-      <c r="N36" s="184"/>
-      <c r="O36" s="184"/>
-      <c r="P36" s="182"/>
-      <c r="Q36" s="182"/>
-      <c r="R36" s="183"/>
-      <c r="S36" s="183"/>
+      <c r="N36" s="181"/>
+      <c r="O36" s="181"/>
+      <c r="P36" s="179"/>
+      <c r="Q36" s="179"/>
+      <c r="R36" s="180"/>
+      <c r="S36" s="180"/>
       <c r="AD36" s="45"/>
       <c r="AE36" s="18"/>
       <c r="AF36" s="18"/>
@@ -7690,15 +7736,15 @@
       <c r="I38" s="80"/>
       <c r="J38" s="76">
         <f>B1</f>
-        <v>179498</v>
+        <v>339674.47768000001</v>
       </c>
       <c r="K38" s="77">
         <f>IF(D1&gt;1,D1/100,D1)</f>
-        <v>0.65689928816999998</v>
+        <v>0.65746340794999991</v>
       </c>
       <c r="L38" s="78">
         <f>J38*K38</f>
-        <v>117912.10842793866</v>
+        <v>223323.53968912899</v>
       </c>
       <c r="M38" s="81"/>
       <c r="N38" s="58"/>
@@ -7724,15 +7770,15 @@
       <c r="I39" s="80"/>
       <c r="J39" s="76">
         <f t="shared" ref="J39:J69" si="0">B2</f>
-        <v>-1732</v>
+        <v>3774.0453121999999</v>
       </c>
       <c r="K39" s="77">
         <f t="shared" ref="K39:K69" si="1">IF(D2&gt;1,D2/100,D2)</f>
-        <v>0.65514753307999996</v>
+        <v>0.65522263839000006</v>
       </c>
       <c r="L39" s="78">
         <f t="shared" ref="L39:L69" si="2">J39*K39</f>
-        <v>-1134.7155272945599</v>
+        <v>2472.8399268630956</v>
       </c>
       <c r="M39" s="80"/>
       <c r="N39" s="58"/>
@@ -7758,15 +7804,15 @@
       <c r="I40" s="79"/>
       <c r="J40" s="76">
         <f t="shared" si="0"/>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="K40" s="77">
         <f t="shared" si="1"/>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="L40" s="78">
         <f t="shared" si="2"/>
-        <v>119046.82395475169</v>
+        <v>220850.6997682222</v>
       </c>
       <c r="M40" s="80"/>
       <c r="N40" s="58"/>
@@ -7826,15 +7872,15 @@
       <c r="I42" s="80"/>
       <c r="J42" s="76">
         <f t="shared" si="0"/>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="K42" s="77">
         <f t="shared" si="1"/>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="L42" s="78">
         <f t="shared" si="2"/>
-        <v>119046.82395475169</v>
+        <v>220850.6997682222</v>
       </c>
       <c r="M42" s="80"/>
       <c r="N42" s="58"/>
@@ -7860,15 +7906,15 @@
       <c r="I43" s="80"/>
       <c r="J43" s="76">
         <f t="shared" si="0"/>
-        <v>1906</v>
+        <v>1664.0298194</v>
       </c>
       <c r="K43" s="77">
         <f t="shared" si="1"/>
-        <v>0.65524048007000002</v>
+        <v>0.65519564517000006</v>
       </c>
       <c r="L43" s="78">
         <f t="shared" si="2"/>
-        <v>1248.8883550134201</v>
+        <v>1090.2650911039016</v>
       </c>
       <c r="M43" s="80"/>
       <c r="N43" s="58"/>
@@ -7894,15 +7940,15 @@
       <c r="I44" s="80"/>
       <c r="J44" s="76">
         <f t="shared" si="0"/>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="K44" s="77">
         <f t="shared" si="1"/>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="L44" s="78">
         <f t="shared" si="2"/>
-        <v>117797.93559999998</v>
+        <v>219760.43467662498</v>
       </c>
       <c r="M44" s="78"/>
       <c r="N44" s="58"/>
@@ -7962,15 +8008,15 @@
       <c r="I46" s="78"/>
       <c r="J46" s="76">
         <f t="shared" si="0"/>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="K46" s="77">
         <f t="shared" si="1"/>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="L46" s="78">
         <f t="shared" si="2"/>
-        <v>117797.93559999998</v>
+        <v>219760.43467662498</v>
       </c>
       <c r="M46" s="81"/>
       <c r="N46" s="58"/>
@@ -8064,15 +8110,15 @@
       <c r="I49" s="80"/>
       <c r="J49" s="76">
         <f t="shared" si="0"/>
-        <v>13056</v>
+        <v>105229.40255</v>
       </c>
       <c r="K49" s="77">
         <f t="shared" si="1"/>
-        <v>0.66326749387000006</v>
+        <v>0.65793525287999999</v>
       </c>
       <c r="L49" s="78">
         <f t="shared" si="2"/>
-        <v>8659.6203999667214</v>
+        <v>69234.133577145563</v>
       </c>
       <c r="M49" s="80"/>
       <c r="N49" s="58"/>
@@ -8098,15 +8144,15 @@
       <c r="I50" s="94"/>
       <c r="J50" s="76">
         <f t="shared" si="0"/>
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="K50" s="77">
         <f t="shared" si="1"/>
-        <v>0.65639999999999998</v>
+        <v>0.6573</v>
       </c>
       <c r="L50" s="78">
         <f t="shared" si="2"/>
-        <v>109138.3152</v>
+        <v>150526.30110000001</v>
       </c>
       <c r="M50" s="80"/>
       <c r="N50" s="58"/>
@@ -8132,15 +8178,15 @@
       <c r="I51" s="80"/>
       <c r="J51" s="76">
         <f t="shared" si="0"/>
-        <v>49366</v>
+        <v>49365.992154</v>
       </c>
       <c r="K51" s="77">
         <f t="shared" si="1"/>
-        <v>0.66156524052999999</v>
+        <v>0.66157444671999999</v>
       </c>
       <c r="L51" s="78">
         <f t="shared" si="2"/>
-        <v>32658.829664003981</v>
+        <v>32659.27894606641</v>
       </c>
       <c r="M51" s="80"/>
       <c r="N51" s="58"/>
@@ -8166,15 +8212,15 @@
       <c r="I52" s="80"/>
       <c r="J52" s="76">
         <f t="shared" si="0"/>
-        <v>-2483</v>
+        <v>-2483.0078454999998</v>
       </c>
       <c r="K52" s="77">
         <f t="shared" si="1"/>
-        <v>0.65752721887999999</v>
+        <v>0.65749415862000005</v>
       </c>
       <c r="L52" s="78">
         <f t="shared" si="2"/>
-        <v>-1632.6400844790401</v>
+        <v>-1632.5631542238814</v>
       </c>
       <c r="M52" s="80"/>
       <c r="N52" s="58"/>
@@ -8198,11 +8244,11 @@
       </c>
       <c r="K53" s="77">
         <f t="shared" si="1"/>
-        <v>0.66137186345999988</v>
+        <v>0.66137904486999999</v>
       </c>
       <c r="L53" s="78">
         <f t="shared" si="2"/>
-        <v>34291.469748537536</v>
+        <v>34291.842097464629</v>
       </c>
       <c r="M53" s="78"/>
       <c r="N53" s="58"/>
@@ -8222,15 +8268,15 @@
       <c r="I54" s="80"/>
       <c r="J54" s="76">
         <f t="shared" si="0"/>
-        <v>-7699.9115773000003</v>
+        <v>-7833.7575975</v>
       </c>
       <c r="K54" s="77">
         <f t="shared" si="1"/>
-        <v>0.65766740619000008</v>
+        <v>0.65768112607999996</v>
       </c>
       <c r="L54" s="78">
         <f t="shared" si="2"/>
-        <v>-5063.9808749352433</v>
+        <v>-5152.1145181615548</v>
       </c>
       <c r="M54" s="80"/>
       <c r="N54" s="58"/>
@@ -8250,15 +8296,15 @@
       <c r="I55" s="80"/>
       <c r="J55" s="76">
         <f t="shared" si="0"/>
-        <v>59548.911576999999</v>
+        <v>59682.757597999997</v>
       </c>
       <c r="K55" s="77">
         <f t="shared" si="1"/>
-        <v>0.66089286234</v>
+        <v>0.66089366851999998</v>
       </c>
       <c r="L55" s="78">
         <f t="shared" si="2"/>
-        <v>39355.450621355092</v>
+        <v>39443.956616332121</v>
       </c>
       <c r="M55" s="80"/>
       <c r="N55" s="58"/>
@@ -8278,15 +8324,15 @@
       <c r="I56" s="80"/>
       <c r="J56" s="76">
         <f t="shared" si="0"/>
-        <v>-1846.0884226999999</v>
+        <v>-1845.9260609</v>
       </c>
       <c r="K56" s="77">
         <f t="shared" si="1"/>
-        <v>0.65780455820000006</v>
+        <v>0.65777149404000002</v>
       </c>
       <c r="L56" s="78">
         <f t="shared" si="2"/>
-        <v>-1214.3653792923085</v>
+        <v>-1214.1975429655652</v>
       </c>
       <c r="M56" s="80"/>
       <c r="N56" s="58"/>
@@ -8306,7 +8352,7 @@
       <c r="I57" s="80"/>
       <c r="J57" s="76">
         <f t="shared" si="0"/>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="K57" s="77">
         <f t="shared" si="1"/>
@@ -8314,7 +8360,7 @@
       </c>
       <c r="L57" s="78">
         <f t="shared" si="2"/>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="M57" s="80"/>
       <c r="N57" s="58"/>
@@ -8362,7 +8408,7 @@
       <c r="I59" s="80"/>
       <c r="J59" s="76">
         <f t="shared" si="0"/>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="K59" s="77">
         <f t="shared" si="1"/>
@@ -8370,7 +8416,7 @@
       </c>
       <c r="L59" s="78">
         <f t="shared" si="2"/>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="M59" s="78"/>
       <c r="N59" s="58"/>
@@ -8419,7 +8465,7 @@
       <c r="I61" s="80"/>
       <c r="J61" s="76">
         <f t="shared" si="0"/>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="K61" s="77">
         <f t="shared" si="1"/>
@@ -8427,7 +8473,7 @@
       </c>
       <c r="L61" s="78">
         <f t="shared" si="2"/>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="M61" s="78"/>
       <c r="N61" s="58"/>
@@ -8477,15 +8523,15 @@
       <c r="I63" s="80"/>
       <c r="J63" s="76">
         <f t="shared" si="0"/>
-        <v>11739</v>
+        <v>-228098.31633999999</v>
       </c>
       <c r="K63" s="77">
         <f t="shared" si="1"/>
-        <v>0.67941201124000006</v>
+        <v>0.65660983710999998</v>
       </c>
       <c r="L63" s="78">
         <f t="shared" si="2"/>
-        <v>7975.6175999463603</v>
+        <v>-149771.59833707265</v>
       </c>
       <c r="M63" s="78"/>
       <c r="N63" s="58"/>
@@ -8505,15 +8551,15 @@
       <c r="I64" s="94"/>
       <c r="J64" s="76">
         <f t="shared" si="0"/>
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="K64" s="77">
         <f t="shared" si="1"/>
-        <v>0.65639999999999998</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="L64" s="78">
         <f t="shared" si="2"/>
-        <v>32594.198399999997</v>
+        <v>190429.7525</v>
       </c>
       <c r="M64" s="80"/>
       <c r="N64" s="58"/>
@@ -8533,15 +8579,15 @@
       <c r="I65" s="80"/>
       <c r="J65" s="76">
         <f t="shared" si="0"/>
-        <v>-2778</v>
+        <v>-46714</v>
       </c>
       <c r="K65" s="77">
         <f t="shared" si="1"/>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="L65" s="78">
         <f t="shared" si="2"/>
-        <v>-1824.1356000077999</v>
+        <v>-30703.721599896679</v>
       </c>
       <c r="M65" s="80"/>
       <c r="N65" s="58"/>
@@ -8561,15 +8607,15 @@
       <c r="I66" s="78"/>
       <c r="J66" s="76">
         <f t="shared" si="0"/>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="K66" s="77">
         <f t="shared" si="1"/>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="L66" s="78">
         <f t="shared" si="2"/>
-        <v>1824.1356000077999</v>
+        <v>30703.721599896679</v>
       </c>
       <c r="M66" s="80"/>
       <c r="N66" s="58"/>
@@ -8616,15 +8662,15 @@
       <c r="I68" s="80"/>
       <c r="J68" s="76">
         <f t="shared" si="0"/>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="K68" s="77">
         <f t="shared" si="1"/>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="L68" s="78">
         <f t="shared" si="2"/>
-        <v>1824.1356000077999</v>
+        <v>30703.721599896679</v>
       </c>
       <c r="M68" s="80"/>
       <c r="N68" s="58"/>
@@ -8642,15 +8688,15 @@
       <c r="I69" s="80"/>
       <c r="J69" s="76">
         <f t="shared" si="0"/>
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="K69" s="77">
         <f t="shared" si="1"/>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="L69" s="78">
         <f t="shared" si="2"/>
-        <v>143556.64919999999</v>
+        <v>371659.77519999997</v>
       </c>
       <c r="M69" s="80"/>
       <c r="N69" s="58"/>
@@ -8685,11 +8731,11 @@
     <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="E72" s="80"/>
       <c r="F72" s="85"/>
-      <c r="G72" s="186"/>
-      <c r="H72" s="186"/>
+      <c r="G72" s="183"/>
+      <c r="H72" s="183"/>
       <c r="I72" s="80"/>
-      <c r="J72" s="186"/>
-      <c r="K72" s="186"/>
+      <c r="J72" s="183"/>
+      <c r="K72" s="183"/>
       <c r="L72" s="80"/>
       <c r="M72" s="80"/>
     </row>
@@ -8919,8 +8965,8 @@
       <c r="K105" s="53"/>
     </row>
     <row r="107" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="G107" s="180"/>
-      <c r="H107" s="180"/>
+      <c r="G107" s="177"/>
+      <c r="H107" s="177"/>
     </row>
     <row r="108" spans="6:11" x14ac:dyDescent="0.2">
       <c r="G108" s="56"/>
@@ -9052,7 +9098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A80B43-80C9-784F-88AA-B65F2CE7D5D9}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -9066,6 +9112,90 @@
         <v>0.01</v>
       </c>
       <c r="D1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2">
+        <v>289626.78000000003</v>
+      </c>
+      <c r="C2">
+        <v>0.65752410482089585</v>
+      </c>
+      <c r="D2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3">
+        <v>229007.11500000002</v>
+      </c>
+      <c r="C3">
+        <v>0.657301820571914</v>
+      </c>
+      <c r="D3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4">
+        <v>50953.72980833333</v>
+      </c>
+      <c r="C4">
+        <v>0.66076269601434134</v>
+      </c>
+      <c r="D4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5">
+        <v>233375.03383500004</v>
+      </c>
+      <c r="C5">
+        <v>0.657301820571914</v>
+      </c>
+      <c r="D5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6">
+        <v>51054</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7">
+        <v>46714.41</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
         <v>0.01</v>
       </c>
     </row>
@@ -9087,20 +9217,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="184" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="F2" s="187" t="s">
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="F2" s="184" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="J2" s="188" t="s">
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="J2" s="185" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="189"/>
+      <c r="K2" s="186"/>
       <c r="L2" s="65"/>
       <c r="M2" s="66" t="s">
         <v>65</v>
@@ -9144,39 +9274,39 @@
       </c>
       <c r="C4" s="3">
         <f>Utilidad!A1</f>
-        <v>179498</v>
+        <v>339786</v>
       </c>
       <c r="D4" s="2">
         <f>IF(Utilidad!C1&gt;1,Utilidad!C1/100,Utilidad!C1)</f>
-        <v>0.66049999999999998</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="F4" s="49" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="3">
         <f>Utilidad!B1</f>
-        <v>179498</v>
+        <v>339674.47768000001</v>
       </c>
       <c r="H4" s="2">
         <f>IF(Utilidad!D1&gt;1,Utilidad!D1/100,Utilidad!D1)</f>
-        <v>0.65689928816999998</v>
+        <v>0.65746340794999991</v>
       </c>
       <c r="J4" s="72">
         <f>+IF(C4&lt;&gt;0,(G4-C4)/C4,ABS(G4-C4))</f>
-        <v>0</v>
+        <v>-3.2821340490776291E-4</v>
       </c>
       <c r="K4" s="72">
         <f>+IF(D4&lt;&gt;0,(H4-D4)/D4,0)</f>
-        <v>-5.4514940651021835E-3</v>
+        <v>-5.9519081493802179E-3</v>
       </c>
       <c r="L4" s="73"/>
       <c r="M4" s="74">
         <f t="shared" ref="M4" si="0">+IF(J4&lt;&gt;"",ABS(J4),0)</f>
-        <v>0</v>
+        <v>3.2821340490776291E-4</v>
       </c>
       <c r="N4" s="75">
         <f>+IF(J4&lt;&gt;"",ABS(K4),0)</f>
-        <v>5.4514940651021835E-3</v>
+        <v>5.9519081493802179E-3</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9185,7 +9315,7 @@
       </c>
       <c r="C5" s="3">
         <f>Utilidad!A2</f>
-        <v>-1732</v>
+        <v>3774</v>
       </c>
       <c r="D5" s="2">
         <f>IF(Utilidad!C2&gt;1,Utilidad!C2/100,Utilidad!C2)</f>
@@ -9196,28 +9326,28 @@
       </c>
       <c r="G5" s="3">
         <f>Utilidad!B2</f>
-        <v>-1732</v>
+        <v>3774.0453121999999</v>
       </c>
       <c r="H5" s="2">
         <f>IF(Utilidad!D2&gt;1,Utilidad!D2/100,Utilidad!D2)</f>
-        <v>0.65514753307999996</v>
+        <v>0.65522263839000006</v>
       </c>
       <c r="J5" s="72">
         <f t="shared" ref="J5:J35" si="1">+IF(C5&lt;&gt;0,(G5-C5)/C5,ABS(G5-C5))</f>
-        <v>0</v>
+        <v>1.2006412294620678E-5</v>
       </c>
       <c r="K5" s="72">
         <f t="shared" ref="K5:K35" si="2">+IF(D5&lt;&gt;0,(H5-D5)/D5,0)</f>
-        <v>-8.0077716727792092E-5</v>
+        <v>3.4551877289455926E-5</v>
       </c>
       <c r="L5" s="73"/>
       <c r="M5" s="74">
         <f t="shared" ref="M5:M35" si="3">+IF(J5&lt;&gt;"",ABS(J5),0)</f>
-        <v>0</v>
+        <v>1.2006412294620678E-5</v>
       </c>
       <c r="N5" s="75">
         <f t="shared" ref="N5:N35" si="4">+IF(J5&lt;&gt;"",ABS(K5),0)</f>
-        <v>8.0077716727792092E-5</v>
+        <v>3.4551877289455926E-5</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9226,7 +9356,7 @@
       </c>
       <c r="C6" s="3">
         <f>Utilidad!A3</f>
-        <v>181230</v>
+        <v>336012</v>
       </c>
       <c r="D6" s="2">
         <f>IF(Utilidad!C3&gt;1,Utilidad!C3/100,Utilidad!C3)</f>
@@ -9237,28 +9367,28 @@
       </c>
       <c r="G6" s="3">
         <f>Utilidad!B3</f>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="H6" s="2">
         <f>IF(Utilidad!D3&gt;1,Utilidad!D3/100,Utilidad!D3)</f>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="J6" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.3203465947646219E-4</v>
       </c>
       <c r="K6" s="72">
         <f t="shared" si="2"/>
-        <v>2.5679896062269624E-3</v>
+        <v>3.492955387667738E-3</v>
       </c>
       <c r="L6" s="73"/>
       <c r="M6" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.3203465947646219E-4</v>
       </c>
       <c r="N6" s="75">
         <f t="shared" si="4"/>
-        <v>2.5679896062269624E-3</v>
+        <v>3.492955387667738E-3</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9308,7 +9438,7 @@
       </c>
       <c r="C8" s="3">
         <f>Utilidad!A5</f>
-        <v>181230</v>
+        <v>336012</v>
       </c>
       <c r="D8" s="2">
         <f>IF(Utilidad!C5&gt;1,Utilidad!C5/100,Utilidad!C5)</f>
@@ -9319,28 +9449,28 @@
       </c>
       <c r="G8" s="3">
         <f>Utilidad!B5</f>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="H8" s="2">
         <f>IF(Utilidad!D5&gt;1,Utilidad!D5/100,Utilidad!D5)</f>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="J8" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.3203465947646219E-4</v>
       </c>
       <c r="K8" s="72">
         <f t="shared" si="2"/>
-        <v>2.5679896062269624E-3</v>
+        <v>3.492955387667738E-3</v>
       </c>
       <c r="L8" s="73"/>
       <c r="M8" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.3203465947646219E-4</v>
       </c>
       <c r="N8" s="75">
         <f t="shared" si="4"/>
-        <v>2.5679896062269624E-3</v>
+        <v>3.492955387667738E-3</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9349,7 +9479,7 @@
       </c>
       <c r="C9" s="3">
         <f>Utilidad!A6</f>
-        <v>1906</v>
+        <v>1664</v>
       </c>
       <c r="D9" s="2">
         <f>IF(Utilidad!C6&gt;1,Utilidad!C6/100,Utilidad!C6)</f>
@@ -9360,28 +9490,28 @@
       </c>
       <c r="G9" s="3">
         <f>Utilidad!B6</f>
-        <v>1906</v>
+        <v>1664.0298194</v>
       </c>
       <c r="H9" s="2">
         <f>IF(Utilidad!D6&gt;1,Utilidad!D6/100,Utilidad!D6)</f>
-        <v>0.65524048007000002</v>
+        <v>0.65519564517000006</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.7920312499970675E-5</v>
       </c>
       <c r="K9" s="72">
         <f t="shared" si="2"/>
-        <v>6.1782768620291802E-5</v>
+        <v>-6.6465659339771914E-6</v>
       </c>
       <c r="L9" s="73"/>
       <c r="M9" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.7920312499970675E-5</v>
       </c>
       <c r="N9" s="75">
         <f t="shared" si="4"/>
-        <v>6.1782768620291802E-5</v>
+        <v>6.6465659339771914E-6</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9390,39 +9520,39 @@
       </c>
       <c r="C10" s="3">
         <f>Utilidad!A7</f>
-        <v>177417</v>
+        <v>332684</v>
       </c>
       <c r="D10" s="2">
         <f>IF(Utilidad!C7&gt;1,Utilidad!C7/100,Utilidad!C7)</f>
-        <v>0.66400000000000003</v>
+        <v>0.66079999999999994</v>
       </c>
       <c r="F10" s="49" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="3">
         <f>Utilidad!B7</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="H10" s="2">
         <f>IF(Utilidad!D7&gt;1,Utilidad!D7/100,Utilidad!D7)</f>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="J10" s="72">
         <f t="shared" si="1"/>
-        <v>1.0748688118951397E-2</v>
+        <v>4.6662975977203557E-3</v>
       </c>
       <c r="K10" s="72">
         <f t="shared" si="2"/>
-        <v>-1.0692771084337509E-2</v>
+        <v>-4.9939467312348209E-3</v>
       </c>
       <c r="L10" s="73"/>
       <c r="M10" s="74">
         <f t="shared" si="3"/>
-        <v>1.0748688118951397E-2</v>
+        <v>4.6662975977203557E-3</v>
       </c>
       <c r="N10" s="75">
         <f t="shared" si="4"/>
-        <v>1.0692771084337509E-2</v>
+        <v>4.9939467312348209E-3</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9472,26 +9602,26 @@
       </c>
       <c r="C12" s="3">
         <f>Utilidad!A9</f>
-        <v>179324</v>
+        <v>334348</v>
       </c>
       <c r="D12" s="2">
         <f>IF(Utilidad!C9&gt;1,Utilidad!C9/100,Utilidad!C9)</f>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="F12" s="49" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3">
         <f>Utilidad!B9</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="H12" s="2">
         <f>IF(Utilidad!D9&gt;1,Utilidad!D9/100,Utilidad!D9)</f>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="J12" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.3377633483676024E-4</v>
       </c>
       <c r="K12" s="72">
         <f t="shared" si="2"/>
@@ -9500,7 +9630,7 @@
       <c r="L12" s="73"/>
       <c r="M12" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.3377633483676024E-4</v>
       </c>
       <c r="N12" s="75">
         <f t="shared" si="4"/>
@@ -9595,39 +9725,39 @@
       </c>
       <c r="C15" s="3">
         <f>Utilidad!A12</f>
-        <v>13055</v>
+        <v>105341</v>
       </c>
       <c r="D15" s="2">
         <f>IF(Utilidad!C12&gt;1,Utilidad!C12/100,Utilidad!C12)</f>
-        <v>0.65639999999999998</v>
+        <v>0.6573</v>
       </c>
       <c r="F15" s="49" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="3">
         <f>Utilidad!B12</f>
-        <v>13056</v>
+        <v>105229.40255</v>
       </c>
       <c r="H15" s="2">
         <f>IF(Utilidad!D12&gt;1,Utilidad!D12/100,Utilidad!D12)</f>
-        <v>0.66326749387000006</v>
+        <v>0.65793525287999999</v>
       </c>
       <c r="J15" s="72">
         <f t="shared" si="1"/>
-        <v>7.6599004212945235E-5</v>
+        <v>-1.0593923543539658E-3</v>
       </c>
       <c r="K15" s="72">
         <f t="shared" si="2"/>
-        <v>1.0462361166971473E-2</v>
+        <v>9.6645805568232519E-4</v>
       </c>
       <c r="L15" s="73"/>
       <c r="M15" s="74">
         <f t="shared" si="3"/>
-        <v>7.6599004212945235E-5</v>
+        <v>1.0593923543539658E-3</v>
       </c>
       <c r="N15" s="75">
         <f t="shared" si="4"/>
-        <v>1.0462361166971473E-2</v>
+        <v>9.6645805568232519E-4</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9636,22 +9766,22 @@
       </c>
       <c r="C16" s="3">
         <f>Utilidad!A13</f>
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="D16" s="2">
         <f>IF(Utilidad!C13&gt;1,Utilidad!C13/100,Utilidad!C13)</f>
-        <v>0.65639999999999998</v>
+        <v>0.6573</v>
       </c>
       <c r="F16" s="49" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="3">
         <f>Utilidad!B13</f>
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="H16" s="2">
         <f>IF(Utilidad!D13&gt;1,Utilidad!D13/100,Utilidad!D13)</f>
-        <v>0.65639999999999998</v>
+        <v>0.6573</v>
       </c>
       <c r="J16" s="72">
         <f t="shared" si="1"/>
@@ -9688,28 +9818,28 @@
       </c>
       <c r="G17" s="3">
         <f>Utilidad!B14</f>
-        <v>49366</v>
+        <v>49365.992154</v>
       </c>
       <c r="H17" s="2">
         <f>IF(Utilidad!D14&gt;1,Utilidad!D14/100,Utilidad!D14)</f>
-        <v>0.66156524052999999</v>
+        <v>0.66157444671999999</v>
       </c>
       <c r="J17" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.5893529960756415E-7</v>
       </c>
       <c r="K17" s="72">
         <f t="shared" si="2"/>
-        <v>-5.6136471817225539E-3</v>
+        <v>-5.5998095295355715E-3</v>
       </c>
       <c r="L17" s="73"/>
       <c r="M17" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5893529960756415E-7</v>
       </c>
       <c r="N17" s="75">
         <f t="shared" si="4"/>
-        <v>5.6136471817225539E-3</v>
+        <v>5.5998095295355715E-3</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9729,28 +9859,28 @@
       </c>
       <c r="G18" s="3">
         <f>Utilidad!B15</f>
-        <v>-2483</v>
+        <v>-2483.0078454999998</v>
       </c>
       <c r="H18" s="2">
         <f>IF(Utilidad!D15&gt;1,Utilidad!D15/100,Utilidad!D15)</f>
-        <v>0.65752721887999999</v>
+        <v>0.65749415862000005</v>
       </c>
       <c r="J18" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.1596858637950044E-6</v>
       </c>
       <c r="K18" s="72">
         <f t="shared" si="2"/>
-        <v>-2.6270506309862421E-4</v>
+        <v>-3.1297153717485911E-4</v>
       </c>
       <c r="L18" s="73"/>
       <c r="M18" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.1596858637950044E-6</v>
       </c>
       <c r="N18" s="75">
         <f t="shared" si="4"/>
-        <v>2.6270506309862421E-4</v>
+        <v>3.1297153717485911E-4</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9774,7 +9904,7 @@
       </c>
       <c r="H19" s="2">
         <f>IF(Utilidad!D16&gt;1,Utilidad!D16/100,Utilidad!D16)</f>
-        <v>0.66137186345999988</v>
+        <v>0.66137904486999999</v>
       </c>
       <c r="J19" s="72">
         <f t="shared" si="1"/>
@@ -9782,7 +9912,7 @@
       </c>
       <c r="K19" s="72">
         <f t="shared" si="2"/>
-        <v>5.5828849931578604E-3</v>
+        <v>5.5938039683746952E-3</v>
       </c>
       <c r="L19" s="73"/>
       <c r="M19" s="74">
@@ -9791,7 +9921,7 @@
       </c>
       <c r="N19" s="75">
         <f t="shared" si="4"/>
-        <v>5.5828849931578604E-3</v>
+        <v>5.5938039683746952E-3</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9800,7 +9930,7 @@
       </c>
       <c r="C20" s="3">
         <f>Utilidad!A17</f>
-        <v>-7700</v>
+        <v>-7836</v>
       </c>
       <c r="D20" s="2">
         <f>IF(Utilidad!C17&gt;1,Utilidad!C17/100,Utilidad!C17)</f>
@@ -9811,28 +9941,28 @@
       </c>
       <c r="G20" s="3">
         <f>Utilidad!B17</f>
-        <v>-7699.9115773000003</v>
+        <v>-7833.7575975</v>
       </c>
       <c r="H20" s="2">
         <f>IF(Utilidad!D17&gt;1,Utilidad!D17/100,Utilidad!D17)</f>
-        <v>0.65766740619000008</v>
+        <v>0.65768112607999996</v>
       </c>
       <c r="J20" s="72">
         <f t="shared" si="1"/>
-        <v>-1.1483467532426319E-5</v>
+        <v>-2.8616673047473525E-4</v>
       </c>
       <c r="K20" s="72">
         <f t="shared" si="2"/>
-        <v>-4.9557260148806692E-5</v>
+        <v>-2.8696852668382906E-5</v>
       </c>
       <c r="L20" s="73"/>
       <c r="M20" s="74">
         <f t="shared" si="3"/>
-        <v>1.1483467532426319E-5</v>
+        <v>2.8616673047473525E-4</v>
       </c>
       <c r="N20" s="75">
         <f t="shared" si="4"/>
-        <v>4.9557260148806692E-5</v>
+        <v>2.8696852668382906E-5</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9841,7 +9971,7 @@
       </c>
       <c r="C21" s="3">
         <f>Utilidad!A18</f>
-        <v>59549</v>
+        <v>59685</v>
       </c>
       <c r="D21" s="2">
         <f>IF(Utilidad!C18&gt;1,Utilidad!C18/100,Utilidad!C18)</f>
@@ -9852,28 +9982,28 @@
       </c>
       <c r="G21" s="3">
         <f>Utilidad!B18</f>
-        <v>59548.911576999999</v>
+        <v>59682.757597999997</v>
       </c>
       <c r="H21" s="2">
         <f>IF(Utilidad!D18&gt;1,Utilidad!D18/100,Utilidad!D18)</f>
-        <v>0.66089286234</v>
+        <v>0.66089366851999998</v>
       </c>
       <c r="J21" s="72">
         <f t="shared" si="1"/>
-        <v>-1.4848779996483151E-6</v>
+        <v>-3.7570612381728979E-5</v>
       </c>
       <c r="K21" s="72">
         <f t="shared" si="2"/>
-        <v>4.8545877147636411E-3</v>
+        <v>4.8558134711875114E-3</v>
       </c>
       <c r="L21" s="73"/>
       <c r="M21" s="74">
         <f t="shared" si="3"/>
-        <v>1.4848779996483151E-6</v>
+        <v>3.7570612381728979E-5</v>
       </c>
       <c r="N21" s="75">
         <f t="shared" si="4"/>
-        <v>4.8545877147636411E-3</v>
+        <v>4.8558134711875114E-3</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9893,28 +10023,28 @@
       </c>
       <c r="G22" s="3">
         <f>Utilidad!B19</f>
-        <v>-1846.0884226999999</v>
+        <v>-1845.9260609</v>
       </c>
       <c r="H22" s="2">
         <f>IF(Utilidad!D19&gt;1,Utilidad!D19/100,Utilidad!D19)</f>
-        <v>0.65780455820000006</v>
+        <v>0.65777149404000002</v>
       </c>
       <c r="J22" s="72">
         <f t="shared" si="1"/>
-        <v>4.7899620801684741E-5</v>
+        <v>-4.005368364028245E-5</v>
       </c>
       <c r="K22" s="72">
         <f t="shared" si="2"/>
-        <v>1.5897552075430199E-4</v>
+        <v>1.0870311692270656E-4</v>
       </c>
       <c r="L22" s="73"/>
       <c r="M22" s="74">
         <f t="shared" si="3"/>
-        <v>4.7899620801684741E-5</v>
+        <v>4.005368364028245E-5</v>
       </c>
       <c r="N22" s="75">
         <f t="shared" si="4"/>
-        <v>1.5897552075430199E-4</v>
+        <v>1.0870311692270656E-4</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -9923,7 +10053,7 @@
       </c>
       <c r="C23" s="3">
         <f>Utilidad!A20</f>
-        <v>61395</v>
+        <v>61531</v>
       </c>
       <c r="D23" s="2">
         <f>IF(Utilidad!C20&gt;1,Utilidad!C20/100,Utilidad!C20)</f>
@@ -9934,7 +10064,7 @@
       </c>
       <c r="G23" s="3">
         <f>Utilidad!B20</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="H23" s="2">
         <f>IF(Utilidad!D20&gt;1,Utilidad!D20/100,Utilidad!D20)</f>
@@ -9942,7 +10072,7 @@
       </c>
       <c r="J23" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.764512197101068E-5</v>
       </c>
       <c r="K23" s="72">
         <f t="shared" si="2"/>
@@ -9951,7 +10081,7 @@
       <c r="L23" s="73"/>
       <c r="M23" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.764512197101068E-5</v>
       </c>
       <c r="N23" s="75">
         <f t="shared" si="4"/>
@@ -10005,7 +10135,7 @@
       </c>
       <c r="C25" s="3">
         <f>Utilidad!A22</f>
-        <v>61395</v>
+        <v>61531</v>
       </c>
       <c r="D25" s="2">
         <f>IF(Utilidad!C22&gt;1,Utilidad!C22/100,Utilidad!C22)</f>
@@ -10016,7 +10146,7 @@
       </c>
       <c r="G25" s="3">
         <f>Utilidad!B22</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="H25" s="2">
         <f>IF(Utilidad!D22&gt;1,Utilidad!D22/100,Utilidad!D22)</f>
@@ -10024,7 +10154,7 @@
       </c>
       <c r="J25" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.764512197101068E-5</v>
       </c>
       <c r="K25" s="72">
         <f t="shared" si="2"/>
@@ -10033,7 +10163,7 @@
       <c r="L25" s="73"/>
       <c r="M25" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.764512197101068E-5</v>
       </c>
       <c r="N25" s="75">
         <f t="shared" si="4"/>
@@ -10098,7 +10228,7 @@
       </c>
       <c r="G27" s="3">
         <f>Utilidad!B24</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="H27" s="2">
         <f>IF(Utilidad!D24&gt;1,Utilidad!D24/100,Utilidad!D24)</f>
@@ -10106,7 +10236,7 @@
       </c>
       <c r="J27" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1774355892173912E-3</v>
       </c>
       <c r="K27" s="72">
         <f t="shared" si="2"/>
@@ -10115,7 +10245,7 @@
       <c r="L27" s="73"/>
       <c r="M27" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.1774355892173912E-3</v>
       </c>
       <c r="N27" s="75">
         <f t="shared" si="4"/>
@@ -10169,7 +10299,7 @@
       </c>
       <c r="C29" s="3">
         <f>Utilidad!A26</f>
-        <v>11739</v>
+        <v>-228232</v>
       </c>
       <c r="D29" s="2">
         <f>IF(Utilidad!C26&gt;1,Utilidad!C26/100,Utilidad!C26)</f>
@@ -10180,28 +10310,28 @@
       </c>
       <c r="G29" s="3">
         <f>Utilidad!B26</f>
-        <v>11739</v>
+        <v>-228098.31633999999</v>
       </c>
       <c r="H29" s="2">
         <f>IF(Utilidad!D26&gt;1,Utilidad!D26/100,Utilidad!D26)</f>
-        <v>0.67941201124000006</v>
+        <v>0.65660983710999998</v>
       </c>
       <c r="J29" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5.8573583020790111E-4</v>
       </c>
       <c r="K29" s="72">
         <f t="shared" si="2"/>
-        <v>2.8165876573850054E-2</v>
+        <v>-6.3410455357142256E-3</v>
       </c>
       <c r="L29" s="73"/>
       <c r="M29" s="74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.8573583020790111E-4</v>
       </c>
       <c r="N29" s="75">
         <f t="shared" si="4"/>
-        <v>2.8165876573850054E-2</v>
+        <v>6.3410455357142256E-3</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -10210,22 +10340,22 @@
       </c>
       <c r="C30" s="3">
         <f>Utilidad!A27</f>
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="D30" s="2">
         <f>IF(Utilidad!C27&gt;1,Utilidad!C27/100,Utilidad!C27)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="F30" s="49" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="3">
         <f>Utilidad!B27</f>
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="H30" s="2">
         <f>IF(Utilidad!D27&gt;1,Utilidad!D27/100,Utilidad!D27)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="J30" s="72">
         <f t="shared" si="1"/>
@@ -10251,22 +10381,22 @@
       </c>
       <c r="C31" s="3">
         <f>Utilidad!A28</f>
-        <v>-2778</v>
+        <v>-46714</v>
       </c>
       <c r="D31" s="2">
         <f>IF(Utilidad!C28&gt;1,Utilidad!C28/100,Utilidad!C28)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="F31" s="49" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="3">
         <f>Utilidad!B28</f>
-        <v>-2778</v>
+        <v>-46714</v>
       </c>
       <c r="H31" s="2">
         <f>IF(Utilidad!D28&gt;1,Utilidad!D28/100,Utilidad!D28)</f>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="J31" s="72">
         <f t="shared" si="1"/>
@@ -10274,7 +10404,7 @@
       </c>
       <c r="K31" s="72">
         <f t="shared" si="2"/>
-        <v>3.5997120658128506E-4</v>
+        <v>-1.9739637967752663E-4</v>
       </c>
       <c r="L31" s="73"/>
       <c r="M31" s="74">
@@ -10283,7 +10413,7 @@
       </c>
       <c r="N31" s="75">
         <f t="shared" si="4"/>
-        <v>3.5997120658128506E-4</v>
+        <v>1.9739637967752663E-4</v>
       </c>
     </row>
     <row r="32" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -10292,22 +10422,22 @@
       </c>
       <c r="C32" s="3">
         <f>Utilidad!A29</f>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="D32" s="2">
         <f>IF(Utilidad!C29&gt;1,Utilidad!C29/100,Utilidad!C29)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="F32" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="3">
         <f>Utilidad!B29</f>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="H32" s="2">
         <f>IF(Utilidad!D29&gt;1,Utilidad!D29/100,Utilidad!D29)</f>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="J32" s="72">
         <f t="shared" si="1"/>
@@ -10315,7 +10445,7 @@
       </c>
       <c r="K32" s="72">
         <f t="shared" si="2"/>
-        <v>3.5997120658128506E-4</v>
+        <v>-1.9739637967752663E-4</v>
       </c>
       <c r="L32" s="73"/>
       <c r="M32" s="74">
@@ -10324,7 +10454,7 @@
       </c>
       <c r="N32" s="75">
         <f t="shared" si="4"/>
-        <v>3.5997120658128506E-4</v>
+        <v>1.9739637967752663E-4</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -10374,22 +10504,22 @@
       </c>
       <c r="C34" s="3">
         <f>Utilidad!A31</f>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="D34" s="2">
         <f>IF(Utilidad!C31&gt;1,Utilidad!C31/100,Utilidad!C31)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="F34" s="49" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="3">
         <f>Utilidad!B31</f>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="H34" s="2">
         <f>IF(Utilidad!D31&gt;1,Utilidad!D31/100,Utilidad!D31)</f>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="J34" s="72">
         <f t="shared" si="1"/>
@@ -10397,7 +10527,7 @@
       </c>
       <c r="K34" s="72">
         <f t="shared" si="2"/>
-        <v>3.5997120658128506E-4</v>
+        <v>-1.9739637967752663E-4</v>
       </c>
       <c r="L34" s="73"/>
       <c r="M34" s="74">
@@ -10406,7 +10536,7 @@
       </c>
       <c r="N34" s="75">
         <f t="shared" si="4"/>
-        <v>3.5997120658128506E-4</v>
+        <v>1.9739637967752663E-4</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -10415,22 +10545,22 @@
       </c>
       <c r="C35" s="3">
         <f>Utilidad!A32</f>
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="D35" s="2">
         <f>IF(Utilidad!C32&gt;1,Utilidad!C32/100,Utilidad!C32)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="F35" s="49" t="s">
         <v>14</v>
       </c>
       <c r="G35" s="3">
         <f>Utilidad!B32</f>
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="H35" s="2">
         <f>IF(Utilidad!D32&gt;1,Utilidad!D32/100,Utilidad!D32)</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="J35" s="72">
         <f t="shared" si="1"/>
@@ -10507,14 +10637,14 @@
       </c>
       <c r="E3" s="9">
         <f>+Utilidad!J38</f>
-        <v>179498</v>
+        <v>339674.47768000001</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>29</v>
       </c>
       <c r="R3" s="9">
         <f>+Utilidad!J51</f>
-        <v>49366</v>
+        <v>49365.992154</v>
       </c>
       <c r="S3" s="10"/>
     </row>
@@ -10522,12 +10652,12 @@
       <c r="B4" s="7"/>
       <c r="E4" s="11">
         <f>+Utilidad!K38</f>
-        <v>0.65689928816999998</v>
+        <v>0.65746340794999991</v>
       </c>
       <c r="P4" s="12"/>
       <c r="R4" s="11">
         <f>+Utilidad!K51</f>
-        <v>0.66156524052999999</v>
+        <v>0.66157444671999999</v>
       </c>
       <c r="S4" s="10"/>
     </row>
@@ -10535,12 +10665,12 @@
       <c r="B5" s="7"/>
       <c r="E5" s="13">
         <f>+Utilidad!L38</f>
-        <v>117912.10842793866</v>
+        <v>223323.53968912899</v>
       </c>
       <c r="P5" s="12"/>
       <c r="R5" s="13">
         <f>+Utilidad!L51</f>
-        <v>32658.829664003981</v>
+        <v>32659.27894606641</v>
       </c>
       <c r="S5" s="10"/>
     </row>
@@ -10549,7 +10679,7 @@
       <c r="P6" s="12"/>
       <c r="R6" s="14">
         <f>+R3-R9</f>
-        <v>-2483</v>
+        <v>-2483.0078460000004</v>
       </c>
       <c r="S6" s="10"/>
     </row>
@@ -10557,12 +10687,12 @@
       <c r="B7" s="7"/>
       <c r="E7" s="14">
         <f>+E3-E10</f>
-        <v>-1732</v>
+        <v>3774.0453100000159</v>
       </c>
       <c r="P7" s="12"/>
       <c r="R7" s="15">
         <f>+Utilidad!K52</f>
-        <v>0.65752721887999999</v>
+        <v>0.65749415862000005</v>
       </c>
       <c r="S7" s="10"/>
     </row>
@@ -10573,14 +10703,14 @@
       </c>
       <c r="E8" s="15">
         <f>+Utilidad!K39</f>
-        <v>0.65514753307999996</v>
+        <v>0.65522263839000006</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>42</v>
       </c>
       <c r="R8" s="16">
         <f>+Utilidad!L52</f>
-        <v>-1632.6400844790401</v>
+        <v>-1632.5631542238814</v>
       </c>
       <c r="S8" s="10"/>
     </row>
@@ -10588,7 +10718,7 @@
       <c r="B9" s="7"/>
       <c r="E9" s="16">
         <f>+Utilidad!L39</f>
-        <v>-1134.7155272945599</v>
+        <v>2472.8399268630956</v>
       </c>
       <c r="P9" s="12"/>
       <c r="R9" s="17">
@@ -10601,13 +10731,13 @@
       <c r="B10" s="7"/>
       <c r="E10" s="17">
         <f>+Utilidad!J40</f>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="G10" s="18"/>
       <c r="P10" s="12"/>
       <c r="R10" s="15">
         <f>+Utilidad!K53</f>
-        <v>0.66137186345999988</v>
+        <v>0.66137904486999999</v>
       </c>
       <c r="S10" s="10"/>
     </row>
@@ -10615,12 +10745,12 @@
       <c r="B11" s="7"/>
       <c r="E11" s="15">
         <f>+Utilidad!K40</f>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="P11" s="12"/>
       <c r="R11" s="19">
         <f>+Utilidad!L53</f>
-        <v>34291.469748537536</v>
+        <v>34291.842097464629</v>
       </c>
       <c r="S11" s="10"/>
     </row>
@@ -10631,7 +10761,7 @@
       </c>
       <c r="E12" s="19">
         <f>+Utilidad!L40</f>
-        <v>119046.82395475169</v>
+        <v>220850.6997682222</v>
       </c>
       <c r="P12" s="12" t="s">
         <v>40</v>
@@ -10642,7 +10772,7 @@
       <c r="B13" s="7"/>
       <c r="R13" s="14">
         <f>+R9-R18</f>
-        <v>-7699.9115769999989</v>
+        <v>-7833.7575979999965</v>
       </c>
       <c r="S13" s="10"/>
     </row>
@@ -10654,7 +10784,7 @@
       </c>
       <c r="R14" s="15">
         <f>+Utilidad!K54</f>
-        <v>0.65766740619000008</v>
+        <v>0.65768112607999996</v>
       </c>
       <c r="S14" s="10"/>
     </row>
@@ -10666,7 +10796,7 @@
       </c>
       <c r="R15" s="21">
         <f>+Utilidad!L54</f>
-        <v>-5063.9808749352433</v>
+        <v>-5152.1145181615548</v>
       </c>
       <c r="S15" s="10"/>
     </row>
@@ -10686,7 +10816,7 @@
       <c r="B18" s="7"/>
       <c r="R18" s="17">
         <f>+Utilidad!J55</f>
-        <v>59548.911576999999</v>
+        <v>59682.757597999997</v>
       </c>
       <c r="S18" s="10"/>
     </row>
@@ -10694,11 +10824,11 @@
       <c r="B19" s="7"/>
       <c r="E19" s="17">
         <f>+Utilidad!J42</f>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="R19" s="15">
         <f>+Utilidad!K53</f>
-        <v>0.66137186345999988</v>
+        <v>0.66137904486999999</v>
       </c>
       <c r="S19" s="10"/>
     </row>
@@ -10706,11 +10836,11 @@
       <c r="B20" s="7"/>
       <c r="E20" s="15">
         <f>+Utilidad!K42</f>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="R20" s="19">
         <f>+Utilidad!L55</f>
-        <v>39355.450621355092</v>
+        <v>39443.956616332121</v>
       </c>
       <c r="S20" s="10"/>
     </row>
@@ -10718,7 +10848,7 @@
       <c r="B21" s="7"/>
       <c r="E21" s="19">
         <f>+Utilidad!L42</f>
-        <v>119046.82395475169</v>
+        <v>220850.6997682222</v>
       </c>
       <c r="S21" s="10"/>
     </row>
@@ -10726,7 +10856,7 @@
       <c r="B22" s="7"/>
       <c r="E22" s="14">
         <f>+E19-E25</f>
-        <v>1906</v>
+        <v>1664.0298199999961</v>
       </c>
       <c r="G22" s="22">
         <f>+Utilidad!J45</f>
@@ -10741,7 +10871,7 @@
       </c>
       <c r="R22" s="14">
         <f>+R18-R25</f>
-        <v>-1846.0884230000011</v>
+        <v>-1845.9260600000052</v>
       </c>
       <c r="S22" s="10"/>
     </row>
@@ -10749,7 +10879,7 @@
       <c r="B23" s="7"/>
       <c r="E23" s="15">
         <f>+Utilidad!K43</f>
-        <v>0.65524048007000002</v>
+        <v>0.65519564517000006</v>
       </c>
       <c r="G23" s="23">
         <f>+Utilidad!K45</f>
@@ -10761,7 +10891,7 @@
       </c>
       <c r="R23" s="15">
         <f>+Utilidad!K56</f>
-        <v>0.65780455820000006</v>
+        <v>0.65777149404000002</v>
       </c>
       <c r="S23" s="10"/>
     </row>
@@ -10769,7 +10899,7 @@
       <c r="B24" s="7"/>
       <c r="E24" s="21">
         <f>+Utilidad!L43</f>
-        <v>1248.8883550134201</v>
+        <v>1090.2650911039016</v>
       </c>
       <c r="G24" s="24">
         <f>+Utilidad!L45</f>
@@ -10781,7 +10911,7 @@
       </c>
       <c r="R24" s="21">
         <f>+Utilidad!L56</f>
-        <v>-1214.3653792923085</v>
+        <v>-1214.1975429655652</v>
       </c>
       <c r="S24" s="10"/>
     </row>
@@ -10792,11 +10922,11 @@
       </c>
       <c r="E25" s="17">
         <f>+Utilidad!J44</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="R25" s="17">
         <f>+Utilidad!J57</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="S25" s="10"/>
     </row>
@@ -10804,7 +10934,7 @@
       <c r="B26" s="7"/>
       <c r="E26" s="15">
         <f>+Utilidad!K44</f>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="R26" s="15">
         <f>+Utilidad!K57</f>
@@ -10816,7 +10946,7 @@
       <c r="B27" s="7"/>
       <c r="E27" s="19">
         <f>+Utilidad!L44</f>
-        <v>117797.93559999998</v>
+        <v>219760.43467662498</v>
       </c>
       <c r="K27" s="25">
         <f>+G22+N22-K29</f>
@@ -10824,7 +10954,7 @@
       </c>
       <c r="R27" s="19">
         <f>+Utilidad!L57</f>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="S27" s="10"/>
     </row>
@@ -10839,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="17">
-        <f>+Utilidad!J66</f>
+        <f>+[2]Utilidad!J66</f>
         <v>2778</v>
       </c>
       <c r="S29" s="10"/>
@@ -10851,12 +10981,12 @@
         <v>0</v>
       </c>
       <c r="K30" s="15">
-        <f>+Utilidad!K66</f>
+        <f>+[2]Utilidad!K66</f>
         <v>0.65663628509999994</v>
       </c>
       <c r="R30" s="17">
         <f>+Utilidad!J59</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="S30" s="10"/>
     </row>
@@ -10864,14 +10994,14 @@
       <c r="B31" s="7"/>
       <c r="E31" s="17">
         <f>+Utilidad!J46</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="G31" s="24">
         <f>+Utilidad!L48</f>
         <v>0</v>
       </c>
       <c r="K31" s="19">
-        <f>+Utilidad!L66</f>
+        <f>+[2]Utilidad!L66</f>
         <v>1824.1356000077999</v>
       </c>
       <c r="R31" s="15">
@@ -10884,14 +11014,14 @@
       <c r="B32" s="7"/>
       <c r="E32" s="15">
         <f>+Utilidad!K46</f>
-        <v>0.65689999999999993</v>
-      </c>
-      <c r="I32" s="203" t="s">
+        <v>0.65749999999999997</v>
+      </c>
+      <c r="I32" s="187" t="s">
         <v>39</v>
       </c>
       <c r="R32" s="19">
         <f>+Utilidad!L59</f>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="S32" s="10"/>
     </row>
@@ -10899,29 +11029,29 @@
       <c r="B33" s="7"/>
       <c r="E33" s="19">
         <f>+Utilidad!L46</f>
-        <v>117797.93559999998</v>
-      </c>
-      <c r="I33" s="203"/>
+        <v>219760.43467662498</v>
+      </c>
+      <c r="I33" s="187"/>
       <c r="K33" s="25">
         <f>+K29-K39</f>
-        <v>0</v>
+        <v>-43936</v>
       </c>
       <c r="S33" s="10"/>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B34" s="7"/>
-      <c r="I34" s="203"/>
+      <c r="I34" s="187"/>
       <c r="K34" s="23">
-        <f>+Utilidad!K67</f>
+        <f>+[2]Utilidad!K67</f>
         <v>0</v>
       </c>
       <c r="S34" s="10"/>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B35" s="7"/>
-      <c r="I35" s="203"/>
+      <c r="I35" s="187"/>
       <c r="K35" s="26">
-        <f>+Utilidad!L67</f>
+        <f>+[2]Utilidad!L67</f>
         <v>0</v>
       </c>
       <c r="M35" s="17">
@@ -10950,7 +11080,7 @@
       <c r="B38" s="7"/>
       <c r="E38" s="17">
         <f>+E31</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="S38" s="10"/>
     </row>
@@ -10958,15 +11088,15 @@
       <c r="B39" s="7"/>
       <c r="E39" s="15">
         <f>+E32</f>
-        <v>0.65689999999999993</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="K39" s="17">
         <f>+Utilidad!J68</f>
-        <v>2778</v>
+        <v>46714</v>
       </c>
       <c r="R39" s="17">
         <f>+Utilidad!J61</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="S39" s="10"/>
     </row>
@@ -10974,19 +11104,19 @@
       <c r="B40" s="7"/>
       <c r="E40" s="19">
         <f>+E33</f>
-        <v>117797.93559999998</v>
+        <v>219760.43467662498</v>
       </c>
       <c r="H40" s="27">
         <f>+Utilidad!J50</f>
-        <v>166268</v>
+        <v>229007</v>
       </c>
       <c r="K40" s="15">
         <f>+Utilidad!K68</f>
-        <v>0.65663628509999994</v>
+        <v>0.65727023161999998</v>
       </c>
       <c r="M40" s="27">
         <f>+Utilidad!J64</f>
-        <v>49656</v>
+        <v>289627</v>
       </c>
       <c r="R40" s="15">
         <f>+Utilidad!K61</f>
@@ -10998,19 +11128,19 @@
       <c r="B41" s="7"/>
       <c r="H41" s="28">
         <f>+Utilidad!K50</f>
-        <v>0.65639999999999998</v>
+        <v>0.6573</v>
       </c>
       <c r="K41" s="19">
         <f>+Utilidad!L68</f>
-        <v>1824.1356000077999</v>
+        <v>30703.721599896679</v>
       </c>
       <c r="M41" s="28">
         <f>+Utilidad!K64</f>
-        <v>0.65639999999999998</v>
+        <v>0.65749999999999997</v>
       </c>
       <c r="R41" s="19">
         <f>+Utilidad!L61</f>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="S41" s="10"/>
     </row>
@@ -11018,19 +11148,19 @@
       <c r="B42" s="7"/>
       <c r="F42" s="14">
         <f>+E38+M35-H40</f>
-        <v>13056</v>
+        <v>105229.40255</v>
       </c>
       <c r="H42" s="29">
         <f>+Utilidad!L50</f>
-        <v>109138.3152</v>
+        <v>150526.30110000001</v>
       </c>
       <c r="M42" s="29">
         <f>+Utilidad!L64</f>
-        <v>32594.198399999997</v>
+        <v>190429.7525</v>
       </c>
       <c r="O42" s="14">
         <f>+R39-M40</f>
-        <v>11739</v>
+        <v>-228098.31634200001</v>
       </c>
       <c r="S42" s="10"/>
     </row>
@@ -11038,11 +11168,11 @@
       <c r="B43" s="7"/>
       <c r="F43" s="15">
         <f>+Utilidad!K49</f>
-        <v>0.66326749387000006</v>
+        <v>0.65793525287999999</v>
       </c>
       <c r="O43" s="15">
         <f>+Utilidad!K63</f>
-        <v>0.67941201124000006</v>
+        <v>0.65660983710999998</v>
       </c>
       <c r="S43" s="10"/>
     </row>
@@ -11050,11 +11180,11 @@
       <c r="B44" s="7"/>
       <c r="F44" s="21">
         <f>+Utilidad!L49</f>
-        <v>8659.6203999667214</v>
+        <v>69234.133577145563</v>
       </c>
       <c r="O44" s="21">
         <f>+Utilidad!L61</f>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="S44" s="10"/>
     </row>
@@ -11062,7 +11192,7 @@
       <c r="B45" s="7"/>
       <c r="K45" s="17">
         <f>+Utilidad!J69</f>
-        <v>218703</v>
+        <v>565348</v>
       </c>
       <c r="O45" s="14"/>
       <c r="S45" s="10"/>
@@ -11071,7 +11201,7 @@
       <c r="B46" s="7"/>
       <c r="K46" s="15">
         <f>+Utilidad!K69</f>
-        <v>0.65639999999999998</v>
+        <v>0.65739999999999998</v>
       </c>
       <c r="S46" s="10"/>
     </row>
@@ -11079,7 +11209,7 @@
       <c r="B47" s="7"/>
       <c r="K47" s="19">
         <f>+Utilidad!L69</f>
-        <v>143556.64919999999</v>
+        <v>371659.77519999997</v>
       </c>
       <c r="S47" s="10"/>
     </row>
@@ -11129,265 +11259,265 @@
       </c>
     </row>
     <row r="56" spans="2:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="G56" s="204" t="s">
+      <c r="G56" s="188" t="s">
         <v>44</v>
       </c>
-      <c r="H56" s="204"/>
-      <c r="I56" s="205"/>
-      <c r="J56" s="206" t="s">
+      <c r="H56" s="188"/>
+      <c r="I56" s="189"/>
+      <c r="J56" s="190" t="s">
         <v>45</v>
       </c>
-      <c r="K56" s="206"/>
-      <c r="L56" s="206"/>
-      <c r="M56" s="207" t="s">
+      <c r="K56" s="190"/>
+      <c r="L56" s="190"/>
+      <c r="M56" s="191" t="s">
         <v>46</v>
       </c>
-      <c r="N56" s="207"/>
-      <c r="O56" s="207"/>
-      <c r="P56" s="207"/>
+      <c r="N56" s="191"/>
+      <c r="O56" s="191"/>
+      <c r="P56" s="191"/>
     </row>
     <row r="57" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G57" s="197" t="s">
+      <c r="G57" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="198"/>
+      <c r="H57" s="193"/>
       <c r="I57" s="34">
         <f>+E3</f>
-        <v>179498</v>
-      </c>
-      <c r="J57" s="192" t="s">
+        <v>339674.47768000001</v>
+      </c>
+      <c r="J57" s="194" t="s">
         <v>52</v>
       </c>
-      <c r="K57" s="192"/>
+      <c r="K57" s="194"/>
       <c r="L57" s="35">
         <f>+Utilidad!J39</f>
-        <v>-1732</v>
-      </c>
-      <c r="M57" s="193" t="s">
+        <v>3774.0453121999999</v>
+      </c>
+      <c r="M57" s="195" t="s">
         <v>51</v>
       </c>
-      <c r="N57" s="193"/>
-      <c r="O57" s="193"/>
+      <c r="N57" s="195"/>
+      <c r="O57" s="195"/>
       <c r="P57" s="35">
         <f>+K45</f>
-        <v>218703</v>
+        <v>565348</v>
       </c>
     </row>
     <row r="58" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G58" s="197" t="s">
+      <c r="G58" s="192" t="s">
         <v>29</v>
       </c>
-      <c r="H58" s="198"/>
+      <c r="H58" s="193"/>
       <c r="I58" s="34">
         <f>+R3</f>
-        <v>49366</v>
-      </c>
-      <c r="J58" s="192" t="s">
-        <v>0</v>
-      </c>
-      <c r="K58" s="192"/>
+        <v>49365.992154</v>
+      </c>
+      <c r="J58" s="194" t="s">
+        <v>0</v>
+      </c>
+      <c r="K58" s="194"/>
       <c r="L58" s="35">
         <f>+Utilidad!J41</f>
         <v>0</v>
       </c>
-      <c r="M58" s="193"/>
-      <c r="N58" s="193"/>
-      <c r="O58" s="193"/>
+      <c r="M58" s="195"/>
+      <c r="N58" s="195"/>
+      <c r="O58" s="195"/>
       <c r="P58" s="35"/>
     </row>
     <row r="59" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G59" s="36"/>
       <c r="H59" s="37"/>
       <c r="I59" s="34"/>
-      <c r="J59" s="192" t="s">
+      <c r="J59" s="194" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="192"/>
+      <c r="K59" s="194"/>
       <c r="L59" s="35">
         <f>+Utilidad!J43</f>
-        <v>1906</v>
-      </c>
-      <c r="M59" s="193"/>
-      <c r="N59" s="193"/>
-      <c r="O59" s="193"/>
+        <v>1664.0298194</v>
+      </c>
+      <c r="M59" s="195"/>
+      <c r="N59" s="195"/>
+      <c r="O59" s="195"/>
       <c r="P59" s="35"/>
     </row>
     <row r="60" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G60" s="36"/>
       <c r="H60" s="37"/>
       <c r="I60" s="34"/>
-      <c r="J60" s="192" t="s">
+      <c r="J60" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="K60" s="192"/>
+      <c r="K60" s="194"/>
       <c r="L60" s="35">
         <v>0</v>
       </c>
-      <c r="M60" s="193"/>
-      <c r="N60" s="193"/>
-      <c r="O60" s="193"/>
+      <c r="M60" s="195"/>
+      <c r="N60" s="195"/>
+      <c r="O60" s="195"/>
       <c r="P60" s="35"/>
     </row>
     <row r="61" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G61" s="36"/>
       <c r="H61" s="37"/>
       <c r="I61" s="34"/>
-      <c r="J61" s="192" t="s">
+      <c r="J61" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="K61" s="192"/>
+      <c r="K61" s="194"/>
       <c r="L61" s="35">
         <f>+Utilidad!J49</f>
-        <v>13056</v>
-      </c>
-      <c r="M61" s="193"/>
-      <c r="N61" s="193"/>
-      <c r="O61" s="193"/>
+        <v>105229.40255</v>
+      </c>
+      <c r="M61" s="195"/>
+      <c r="N61" s="195"/>
+      <c r="O61" s="195"/>
       <c r="P61" s="35"/>
     </row>
     <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G62" s="36"/>
       <c r="H62" s="37"/>
       <c r="I62" s="34"/>
-      <c r="J62" s="192" t="s">
+      <c r="J62" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="K62" s="192"/>
+      <c r="K62" s="194"/>
       <c r="L62" s="35">
         <f>+Utilidad!J52</f>
-        <v>-2483</v>
-      </c>
-      <c r="M62" s="193"/>
-      <c r="N62" s="193"/>
-      <c r="O62" s="193"/>
+        <v>-2483.0078454999998</v>
+      </c>
+      <c r="M62" s="195"/>
+      <c r="N62" s="195"/>
+      <c r="O62" s="195"/>
       <c r="P62" s="35"/>
     </row>
     <row r="63" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G63" s="36"/>
       <c r="H63" s="37"/>
       <c r="I63" s="34"/>
-      <c r="J63" s="192" t="s">
+      <c r="J63" s="194" t="s">
         <v>55</v>
       </c>
-      <c r="K63" s="192"/>
+      <c r="K63" s="194"/>
       <c r="L63" s="35">
         <f>+Utilidad!J54</f>
-        <v>-7699.9115773000003</v>
-      </c>
-      <c r="M63" s="193"/>
-      <c r="N63" s="193"/>
-      <c r="O63" s="193"/>
+        <v>-7833.7575975</v>
+      </c>
+      <c r="M63" s="195"/>
+      <c r="N63" s="195"/>
+      <c r="O63" s="195"/>
       <c r="P63" s="35"/>
     </row>
     <row r="64" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G64" s="36"/>
       <c r="H64" s="37"/>
       <c r="I64" s="34"/>
-      <c r="J64" s="192" t="s">
+      <c r="J64" s="194" t="s">
         <v>38</v>
       </c>
-      <c r="K64" s="192"/>
+      <c r="K64" s="194"/>
       <c r="L64" s="35">
         <f>+Utilidad!J56</f>
-        <v>-1846.0884226999999</v>
-      </c>
-      <c r="M64" s="193"/>
-      <c r="N64" s="193"/>
-      <c r="O64" s="193"/>
+        <v>-1845.9260609</v>
+      </c>
+      <c r="M64" s="195"/>
+      <c r="N64" s="195"/>
+      <c r="O64" s="195"/>
       <c r="P64" s="35"/>
     </row>
     <row r="65" spans="7:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G65" s="36"/>
       <c r="H65" s="37"/>
       <c r="I65" s="34"/>
-      <c r="J65" s="192" t="s">
+      <c r="J65" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="K65" s="192"/>
+      <c r="K65" s="194"/>
       <c r="L65" s="35">
         <v>0</v>
       </c>
-      <c r="M65" s="193"/>
-      <c r="N65" s="193"/>
-      <c r="O65" s="193"/>
+      <c r="M65" s="195"/>
+      <c r="N65" s="195"/>
+      <c r="O65" s="195"/>
       <c r="P65" s="35"/>
     </row>
     <row r="66" spans="7:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G66" s="36"/>
       <c r="H66" s="37"/>
       <c r="I66" s="34"/>
-      <c r="J66" s="192" t="s">
+      <c r="J66" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="K66" s="192"/>
+      <c r="K66" s="194"/>
       <c r="L66" s="35">
         <f>+Utilidad!J63</f>
-        <v>11739</v>
-      </c>
-      <c r="M66" s="193"/>
-      <c r="N66" s="193"/>
-      <c r="O66" s="193"/>
+        <v>-228098.31633999999</v>
+      </c>
+      <c r="M66" s="195"/>
+      <c r="N66" s="195"/>
+      <c r="O66" s="195"/>
       <c r="P66" s="35"/>
     </row>
     <row r="67" spans="7:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G67" s="197"/>
-      <c r="H67" s="198"/>
+      <c r="G67" s="192"/>
+      <c r="H67" s="193"/>
       <c r="I67" s="34"/>
-      <c r="J67" s="192" t="s">
+      <c r="J67" s="194" t="s">
         <v>59</v>
       </c>
-      <c r="K67" s="192"/>
+      <c r="K67" s="194"/>
       <c r="L67" s="35">
         <f>+K27</f>
         <v>-2778</v>
       </c>
-      <c r="M67" s="193"/>
-      <c r="N67" s="193"/>
-      <c r="O67" s="193"/>
+      <c r="M67" s="195"/>
+      <c r="N67" s="195"/>
+      <c r="O67" s="195"/>
       <c r="P67" s="35"/>
     </row>
     <row r="68" spans="7:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G68" s="190"/>
-      <c r="H68" s="191"/>
+      <c r="G68" s="196"/>
+      <c r="H68" s="197"/>
       <c r="I68" s="34"/>
-      <c r="J68" s="192" t="s">
+      <c r="J68" s="194" t="s">
         <v>60</v>
       </c>
-      <c r="K68" s="192"/>
+      <c r="K68" s="194"/>
       <c r="L68" s="35">
         <f>+K33</f>
-        <v>0</v>
-      </c>
-      <c r="M68" s="193"/>
-      <c r="N68" s="193"/>
-      <c r="O68" s="193"/>
+        <v>-43936</v>
+      </c>
+      <c r="M68" s="195"/>
+      <c r="N68" s="195"/>
+      <c r="O68" s="195"/>
       <c r="P68" s="35"/>
     </row>
     <row r="69" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G69" s="194" t="s">
+      <c r="G69" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="H69" s="195"/>
+      <c r="H69" s="199"/>
       <c r="I69" s="38">
         <f>+SUM(I57:I68)</f>
-        <v>228864</v>
-      </c>
-      <c r="J69" s="196" t="s">
+        <v>389040.46983399999</v>
+      </c>
+      <c r="J69" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="K69" s="196"/>
+      <c r="K69" s="200"/>
       <c r="L69" s="39">
         <f>+SUM(L57:L68)</f>
-        <v>10162</v>
-      </c>
-      <c r="M69" s="196" t="s">
+        <v>-176307.53016230001</v>
+      </c>
+      <c r="M69" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="N69" s="196"/>
-      <c r="O69" s="196"/>
+      <c r="N69" s="200"/>
+      <c r="O69" s="200"/>
       <c r="P69" s="38">
         <f>+SUM(P57:P68)</f>
-        <v>218703</v>
+        <v>565348</v>
       </c>
     </row>
     <row r="71" spans="7:16" ht="19" x14ac:dyDescent="0.2">
@@ -11399,7 +11529,7 @@
       <c r="O71" s="41"/>
       <c r="P71" s="43">
         <f>+I69-L69-P69</f>
-        <v>-1</v>
+        <v>-3.7000281736254692E-6</v>
       </c>
     </row>
     <row r="74" spans="7:16" ht="16" x14ac:dyDescent="0.2">
@@ -11408,265 +11538,265 @@
       </c>
     </row>
     <row r="75" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G75" s="199" t="s">
+      <c r="G75" s="201" t="s">
         <v>44</v>
       </c>
-      <c r="H75" s="199"/>
-      <c r="I75" s="200"/>
-      <c r="J75" s="201" t="s">
+      <c r="H75" s="201"/>
+      <c r="I75" s="202"/>
+      <c r="J75" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="K75" s="201"/>
-      <c r="L75" s="201"/>
-      <c r="M75" s="202" t="s">
+      <c r="K75" s="203"/>
+      <c r="L75" s="203"/>
+      <c r="M75" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="N75" s="202"/>
-      <c r="O75" s="202"/>
-      <c r="P75" s="202"/>
+      <c r="N75" s="204"/>
+      <c r="O75" s="204"/>
+      <c r="P75" s="204"/>
     </row>
     <row r="76" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G76" s="197" t="s">
+      <c r="G76" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="H76" s="198"/>
+      <c r="H76" s="193"/>
       <c r="I76" s="34">
         <f>+E5</f>
-        <v>117912.10842793866</v>
-      </c>
-      <c r="J76" s="192" t="s">
+        <v>223323.53968912899</v>
+      </c>
+      <c r="J76" s="194" t="s">
         <v>52</v>
       </c>
-      <c r="K76" s="192"/>
+      <c r="K76" s="194"/>
       <c r="L76" s="35">
         <f>+Utilidad!L39</f>
-        <v>-1134.7155272945599</v>
-      </c>
-      <c r="M76" s="193" t="s">
+        <v>2472.8399268630956</v>
+      </c>
+      <c r="M76" s="195" t="s">
         <v>51</v>
       </c>
-      <c r="N76" s="193"/>
-      <c r="O76" s="193"/>
+      <c r="N76" s="195"/>
+      <c r="O76" s="195"/>
       <c r="P76" s="35">
         <f>+K47</f>
-        <v>143556.64919999999</v>
+        <v>371659.77519999997</v>
       </c>
     </row>
     <row r="77" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G77" s="197" t="s">
+      <c r="G77" s="192" t="s">
         <v>29</v>
       </c>
-      <c r="H77" s="198"/>
+      <c r="H77" s="193"/>
       <c r="I77" s="34">
         <f>+R5</f>
-        <v>32658.829664003981</v>
-      </c>
-      <c r="J77" s="192" t="s">
-        <v>0</v>
-      </c>
-      <c r="K77" s="192"/>
+        <v>32659.27894606641</v>
+      </c>
+      <c r="J77" s="194" t="s">
+        <v>0</v>
+      </c>
+      <c r="K77" s="194"/>
       <c r="L77" s="35">
         <f>+Utilidad!L41</f>
         <v>0</v>
       </c>
-      <c r="M77" s="193"/>
-      <c r="N77" s="193"/>
-      <c r="O77" s="193"/>
+      <c r="M77" s="195"/>
+      <c r="N77" s="195"/>
+      <c r="O77" s="195"/>
       <c r="P77" s="35"/>
     </row>
     <row r="78" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G78" s="36"/>
       <c r="H78" s="37"/>
       <c r="I78" s="34"/>
-      <c r="J78" s="192" t="s">
+      <c r="J78" s="194" t="s">
         <v>37</v>
       </c>
-      <c r="K78" s="192"/>
+      <c r="K78" s="194"/>
       <c r="L78" s="35">
         <f>+Utilidad!L43</f>
-        <v>1248.8883550134201</v>
-      </c>
-      <c r="M78" s="193"/>
-      <c r="N78" s="193"/>
-      <c r="O78" s="193"/>
+        <v>1090.2650911039016</v>
+      </c>
+      <c r="M78" s="195"/>
+      <c r="N78" s="195"/>
+      <c r="O78" s="195"/>
       <c r="P78" s="35"/>
     </row>
     <row r="79" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G79" s="36"/>
       <c r="H79" s="37"/>
       <c r="I79" s="34"/>
-      <c r="J79" s="192" t="s">
+      <c r="J79" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="K79" s="192"/>
+      <c r="K79" s="194"/>
       <c r="L79" s="35">
         <v>0</v>
       </c>
-      <c r="M79" s="193"/>
-      <c r="N79" s="193"/>
-      <c r="O79" s="193"/>
+      <c r="M79" s="195"/>
+      <c r="N79" s="195"/>
+      <c r="O79" s="195"/>
       <c r="P79" s="35"/>
     </row>
     <row r="80" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G80" s="36"/>
       <c r="H80" s="37"/>
       <c r="I80" s="34"/>
-      <c r="J80" s="192" t="s">
+      <c r="J80" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="K80" s="192"/>
+      <c r="K80" s="194"/>
       <c r="L80" s="35">
         <f>+Utilidad!L49</f>
-        <v>8659.6203999667214</v>
-      </c>
-      <c r="M80" s="193"/>
-      <c r="N80" s="193"/>
-      <c r="O80" s="193"/>
+        <v>69234.133577145563</v>
+      </c>
+      <c r="M80" s="195"/>
+      <c r="N80" s="195"/>
+      <c r="O80" s="195"/>
       <c r="P80" s="35"/>
     </row>
     <row r="81" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G81" s="36"/>
       <c r="H81" s="37"/>
       <c r="I81" s="34"/>
-      <c r="J81" s="192" t="s">
+      <c r="J81" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="K81" s="192"/>
+      <c r="K81" s="194"/>
       <c r="L81" s="35">
         <f>+Utilidad!L52</f>
-        <v>-1632.6400844790401</v>
-      </c>
-      <c r="M81" s="193"/>
-      <c r="N81" s="193"/>
-      <c r="O81" s="193"/>
+        <v>-1632.5631542238814</v>
+      </c>
+      <c r="M81" s="195"/>
+      <c r="N81" s="195"/>
+      <c r="O81" s="195"/>
       <c r="P81" s="35"/>
     </row>
     <row r="82" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G82" s="36"/>
       <c r="H82" s="37"/>
       <c r="I82" s="34"/>
-      <c r="J82" s="192" t="s">
+      <c r="J82" s="194" t="s">
         <v>55</v>
       </c>
-      <c r="K82" s="192"/>
+      <c r="K82" s="194"/>
       <c r="L82" s="35">
         <f>+Utilidad!L54</f>
-        <v>-5063.9808749352433</v>
-      </c>
-      <c r="M82" s="193"/>
-      <c r="N82" s="193"/>
-      <c r="O82" s="193"/>
+        <v>-5152.1145181615548</v>
+      </c>
+      <c r="M82" s="195"/>
+      <c r="N82" s="195"/>
+      <c r="O82" s="195"/>
       <c r="P82" s="35"/>
     </row>
     <row r="83" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G83" s="36"/>
       <c r="H83" s="37"/>
       <c r="I83" s="34"/>
-      <c r="J83" s="192" t="s">
+      <c r="J83" s="194" t="s">
         <v>38</v>
       </c>
-      <c r="K83" s="192"/>
+      <c r="K83" s="194"/>
       <c r="L83" s="35">
         <f>+Utilidad!L56</f>
-        <v>-1214.3653792923085</v>
-      </c>
-      <c r="M83" s="193"/>
-      <c r="N83" s="193"/>
-      <c r="O83" s="193"/>
+        <v>-1214.1975429655652</v>
+      </c>
+      <c r="M83" s="195"/>
+      <c r="N83" s="195"/>
+      <c r="O83" s="195"/>
       <c r="P83" s="35"/>
     </row>
     <row r="84" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G84" s="36"/>
       <c r="H84" s="37"/>
       <c r="I84" s="34"/>
-      <c r="J84" s="192" t="s">
+      <c r="J84" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="K84" s="192"/>
+      <c r="K84" s="194"/>
       <c r="L84" s="35">
         <v>0</v>
       </c>
-      <c r="M84" s="193"/>
-      <c r="N84" s="193"/>
-      <c r="O84" s="193"/>
+      <c r="M84" s="195"/>
+      <c r="N84" s="195"/>
+      <c r="O84" s="195"/>
       <c r="P84" s="35"/>
     </row>
     <row r="85" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G85" s="36"/>
       <c r="H85" s="37"/>
       <c r="I85" s="34"/>
-      <c r="J85" s="192" t="s">
+      <c r="J85" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="K85" s="192"/>
+      <c r="K85" s="194"/>
       <c r="L85" s="35">
         <f>+Utilidad!L63</f>
-        <v>7975.6175999463603</v>
-      </c>
-      <c r="M85" s="193"/>
-      <c r="N85" s="193"/>
-      <c r="O85" s="193"/>
+        <v>-149771.59833707265</v>
+      </c>
+      <c r="M85" s="195"/>
+      <c r="N85" s="195"/>
+      <c r="O85" s="195"/>
       <c r="P85" s="35"/>
     </row>
     <row r="86" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G86" s="197"/>
-      <c r="H86" s="198"/>
+      <c r="G86" s="192"/>
+      <c r="H86" s="193"/>
       <c r="I86" s="34"/>
-      <c r="J86" s="192" t="s">
+      <c r="J86" s="194" t="s">
         <v>59</v>
       </c>
-      <c r="K86" s="192"/>
+      <c r="K86" s="194"/>
       <c r="L86" s="35">
         <f>+Utilidad!L65</f>
-        <v>-1824.1356000077999</v>
-      </c>
-      <c r="M86" s="193"/>
-      <c r="N86" s="193"/>
-      <c r="O86" s="193"/>
+        <v>-30703.721599896679</v>
+      </c>
+      <c r="M86" s="195"/>
+      <c r="N86" s="195"/>
+      <c r="O86" s="195"/>
       <c r="P86" s="35"/>
     </row>
     <row r="87" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G87" s="190"/>
-      <c r="H87" s="191"/>
+      <c r="G87" s="196"/>
+      <c r="H87" s="197"/>
       <c r="I87" s="34"/>
-      <c r="J87" s="192" t="s">
+      <c r="J87" s="194" t="s">
         <v>60</v>
       </c>
-      <c r="K87" s="192"/>
+      <c r="K87" s="194"/>
       <c r="L87" s="35">
         <f>+Utilidad!L67</f>
         <v>0</v>
       </c>
-      <c r="M87" s="193"/>
-      <c r="N87" s="193"/>
-      <c r="O87" s="193"/>
+      <c r="M87" s="195"/>
+      <c r="N87" s="195"/>
+      <c r="O87" s="195"/>
       <c r="P87" s="35"/>
     </row>
     <row r="88" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G88" s="194" t="s">
+      <c r="G88" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="H88" s="195"/>
+      <c r="H88" s="199"/>
       <c r="I88" s="38">
         <f>+SUM(I76:I87)</f>
-        <v>150570.93809194263</v>
-      </c>
-      <c r="J88" s="196" t="s">
+        <v>255982.81863519541</v>
+      </c>
+      <c r="J88" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="K88" s="196"/>
+      <c r="K88" s="200"/>
       <c r="L88" s="39">
         <f>+SUM(L76:L87)</f>
-        <v>7014.2888889175501</v>
-      </c>
-      <c r="M88" s="196" t="s">
+        <v>-115676.95655720777</v>
+      </c>
+      <c r="M88" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="N88" s="196"/>
-      <c r="O88" s="196"/>
+      <c r="N88" s="200"/>
+      <c r="O88" s="200"/>
       <c r="P88" s="38">
         <f>+SUM(P76:P87)</f>
-        <v>143556.64919999999</v>
+        <v>371659.77519999997</v>
       </c>
     </row>
     <row r="90" spans="7:16" ht="19" x14ac:dyDescent="0.2">
@@ -11678,18 +11808,57 @@
       <c r="O90" s="41"/>
       <c r="P90" s="43">
         <f>+I88-L88-P88</f>
-        <v>3.0251103453338146E-6</v>
+        <v>-7.5967982411384583E-6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="I32:I35"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="M56:P56"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="M57:O57"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="M87:O87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="M88:O88"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="M85:O85"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="M86:O86"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="M82:O82"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="M83:O83"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="M84:O84"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="M79:O79"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="M80:O80"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="M81:O81"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="M77:O77"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="M78:O78"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="M75:P75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="M76:O76"/>
+    <mergeCell ref="M63:O63"/>
+    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="M65:O65"/>
+    <mergeCell ref="M66:O66"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="M69:O69"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="J58:K58"/>
     <mergeCell ref="M58:O58"/>
@@ -11706,52 +11875,13 @@
     <mergeCell ref="M62:O62"/>
     <mergeCell ref="J63:K63"/>
     <mergeCell ref="J64:K64"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="M69:O69"/>
-    <mergeCell ref="M63:O63"/>
-    <mergeCell ref="M64:O64"/>
-    <mergeCell ref="J65:K65"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="M65:O65"/>
-    <mergeCell ref="M66:O66"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="M75:P75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="M76:O76"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="M77:O77"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="M78:O78"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="M79:O79"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="M80:O80"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="M81:O81"/>
-    <mergeCell ref="J82:K82"/>
-    <mergeCell ref="M82:O82"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="M83:O83"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="M84:O84"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="M85:O85"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="M86:O86"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="M87:O87"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="M88:O88"/>
+    <mergeCell ref="I32:I35"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="M57:O57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11759,7 +11889,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{F9CC1162-4D85-466B-BC5A-6E504FA05EC9}">
+          <x14:cfRule type="iconSet" priority="10" id="{F9CC1162-4D85-466B-BC5A-6E504FA05EC9}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11778,7 +11908,7 @@
           <xm:sqref>E7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{52C0BEA9-D4D9-47CA-B868-DA562EEE37B5}">
+          <x14:cfRule type="iconSet" priority="9" id="{52C0BEA9-D4D9-47CA-B868-DA562EEE37B5}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11797,7 +11927,7 @@
           <xm:sqref>E14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{6DE9E117-B614-485D-83F5-5CAB58EC93AD}">
+          <x14:cfRule type="iconSet" priority="8" id="{6DE9E117-B614-485D-83F5-5CAB58EC93AD}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11816,7 +11946,7 @@
           <xm:sqref>E22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{36A7A1E3-D695-4B26-A0F4-CC82340F1E7D}">
+          <x14:cfRule type="iconSet" priority="7" id="{36A7A1E3-D695-4B26-A0F4-CC82340F1E7D}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11835,7 +11965,140 @@
           <xm:sqref>F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{5AF22969-E570-4E96-AAA9-DC2A0C331BB9}">
+          <x14:cfRule type="iconSet" priority="5" id="{B01FD190-62BE-4459-B2A0-716D9802C413}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{550657F3-BE2F-4861-ACC6-5ACBB0C0BA61}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L88</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="14" id="{C66335D4-AA50-46BC-AD3C-CACD6C42245F}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>O42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="15" id="{9129E902-8FA5-474F-8BAB-4FF269580EEC}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>O45</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="11" id="{2375EB51-8EF9-4BA6-930D-FF8EFCF70FB7}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>R6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="12" id="{B9933F35-6337-4D2A-87D0-7EE60258E2E2}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>R13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="13" id="{7B3F2F6E-3593-4FC2-A036-11A408837EF5}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>R22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{9875C1F0-16F5-1041-ADE6-7B4FDE31E57F}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11854,7 +12117,7 @@
           <xm:sqref>K27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{70A9D3FD-EA46-4078-A0C1-99D155C7D8A2}">
+          <x14:cfRule type="iconSet" priority="2" id="{B61EA57E-2A12-374B-A93E-1F69F4F35CE7}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -11871,139 +12134,6 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>K33</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{B01FD190-62BE-4459-B2A0-716D9802C413}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L69</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{550657F3-BE2F-4861-ACC6-5ACBB0C0BA61}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L88</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{C66335D4-AA50-46BC-AD3C-CACD6C42245F}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>O42</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{9129E902-8FA5-474F-8BAB-4FF269580EEC}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>O45</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{2375EB51-8EF9-4BA6-930D-FF8EFCF70FB7}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>R6</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{B9933F35-6337-4D2A-87D0-7EE60258E2E2}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>R13</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{7B3F2F6E-3593-4FC2-A036-11A408837EF5}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>R22</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -12041,18 +12171,18 @@
       <c r="E8" s="99"/>
     </row>
     <row r="9" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C9" s="211" t="s">
+      <c r="C9" s="214" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="212"/>
-      <c r="E9" s="213"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="216"/>
     </row>
     <row r="10" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C10" s="211" t="s">
+      <c r="C10" s="214" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="212"/>
-      <c r="E10" s="213"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="216"/>
     </row>
     <row r="11" spans="3:5" ht="19" x14ac:dyDescent="0.3">
       <c r="C11" s="208" t="s">
@@ -12062,25 +12192,25 @@
       <c r="E11" s="210"/>
     </row>
     <row r="12" spans="3:5" ht="17" x14ac:dyDescent="0.25">
-      <c r="C12" s="217" t="s">
+      <c r="C12" s="211" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="218"/>
-      <c r="E12" s="219"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="213"/>
     </row>
     <row r="13" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C13" s="211" t="s">
+      <c r="C13" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="212"/>
-      <c r="E13" s="213"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="216"/>
     </row>
     <row r="14" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C14" s="211" t="s">
+      <c r="C14" s="214" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="213"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="216"/>
     </row>
     <row r="15" spans="3:5" ht="19" x14ac:dyDescent="0.3">
       <c r="C15" s="97" t="s">
@@ -12097,35 +12227,40 @@
       <c r="E16" s="210"/>
     </row>
     <row r="17" spans="3:5" ht="17" x14ac:dyDescent="0.25">
-      <c r="C17" s="217" t="s">
+      <c r="C17" s="211" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="218"/>
-      <c r="E17" s="219"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="213"/>
     </row>
     <row r="18" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C18" s="211" t="s">
+      <c r="C18" s="214" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="212"/>
-      <c r="E18" s="213"/>
+      <c r="D18" s="215"/>
+      <c r="E18" s="216"/>
     </row>
     <row r="19" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C19" s="211" t="s">
+      <c r="C19" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="212"/>
-      <c r="E19" s="213"/>
+      <c r="D19" s="215"/>
+      <c r="E19" s="216"/>
     </row>
     <row r="20" spans="3:5" ht="19" x14ac:dyDescent="0.3">
-      <c r="C20" s="214" t="s">
+      <c r="C20" s="205" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="215"/>
-      <c r="E20" s="216"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
@@ -12133,11 +12268,6 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14732,86 +14862,86 @@
     <row r="2" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B2" s="105"/>
       <c r="C2" s="106"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="236" t="s">
+      <c r="D2" s="270"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="276" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="237"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="276"/>
+      <c r="I2" s="276"/>
+      <c r="J2" s="276"/>
+      <c r="K2" s="276"/>
+      <c r="L2" s="276"/>
+      <c r="M2" s="276"/>
+      <c r="N2" s="276"/>
+      <c r="O2" s="276"/>
+      <c r="P2" s="276"/>
+      <c r="Q2" s="277"/>
       <c r="R2" s="107"/>
     </row>
     <row r="3" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B3" s="105"/>
       <c r="C3" s="106"/>
-      <c r="D3" s="232"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="M3" s="238"/>
-      <c r="N3" s="238"/>
-      <c r="O3" s="238"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="239"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
+      <c r="H3" s="278"/>
+      <c r="I3" s="278"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="278"/>
+      <c r="M3" s="278"/>
+      <c r="N3" s="278"/>
+      <c r="O3" s="278"/>
+      <c r="P3" s="278"/>
+      <c r="Q3" s="279"/>
       <c r="R3" s="107"/>
     </row>
     <row r="4" spans="2:20" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="105"/>
       <c r="C4" s="106"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="238" t="s">
+      <c r="D4" s="272"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="278" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="M4" s="238" t="s">
+      <c r="G4" s="278"/>
+      <c r="H4" s="278"/>
+      <c r="I4" s="278"/>
+      <c r="J4" s="278"/>
+      <c r="K4" s="278"/>
+      <c r="L4" s="278"/>
+      <c r="M4" s="278" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="238"/>
+      <c r="N4" s="278"/>
       <c r="O4" s="108"/>
-      <c r="P4" s="241">
+      <c r="P4" s="281">
         <f ca="1">TODAY()</f>
         <v>45546</v>
       </c>
-      <c r="Q4" s="242"/>
+      <c r="Q4" s="282"/>
       <c r="R4" s="107"/>
     </row>
     <row r="5" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="105"/>
       <c r="C5" s="106"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="M5" s="240"/>
-      <c r="N5" s="240"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="275"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+      <c r="I5" s="280"/>
+      <c r="J5" s="280"/>
+      <c r="K5" s="280"/>
+      <c r="L5" s="280"/>
+      <c r="M5" s="280"/>
+      <c r="N5" s="280"/>
       <c r="O5" s="109"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="244"/>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="284"/>
       <c r="R5" s="107"/>
     </row>
     <row r="6" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
@@ -14834,20 +14964,20 @@
     <row r="7" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="112"/>
       <c r="C7" s="113"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="224"/>
-      <c r="H7" s="225"/>
+      <c r="D7" s="260"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="264"/>
+      <c r="H7" s="265"/>
       <c r="I7" s="114"/>
       <c r="J7" s="115"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="227"/>
-      <c r="M7" s="227"/>
-      <c r="N7" s="224" t="s">
+      <c r="K7" s="266"/>
+      <c r="L7" s="267"/>
+      <c r="M7" s="267"/>
+      <c r="N7" s="264" t="s">
         <v>84</v>
       </c>
-      <c r="O7" s="225"/>
+      <c r="O7" s="265"/>
       <c r="P7" s="114" t="s">
         <v>85</v>
       </c>
@@ -14859,22 +14989,22 @@
     <row r="8" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="112"/>
       <c r="C8" s="113"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="224" t="s">
+      <c r="D8" s="262"/>
+      <c r="E8" s="263"/>
+      <c r="F8" s="263"/>
+      <c r="G8" s="264" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="225"/>
+      <c r="H8" s="265"/>
       <c r="I8" s="114" t="s">
         <v>85</v>
       </c>
       <c r="J8" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="K8" s="228"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
+      <c r="K8" s="268"/>
+      <c r="L8" s="269"/>
+      <c r="M8" s="269"/>
       <c r="N8" s="116" t="s">
         <v>15</v>
       </c>
@@ -14892,24 +15022,24 @@
     <row r="9" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="112"/>
       <c r="C9" s="113"/>
-      <c r="D9" s="245" t="s">
+      <c r="D9" s="256" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="248" t="s">
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="249"/>
-      <c r="O9" s="249"/>
-      <c r="P9" s="249"/>
-      <c r="Q9" s="250"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
+      <c r="Q9" s="259"/>
       <c r="R9" s="107"/>
     </row>
     <row r="10" spans="2:20" ht="14" x14ac:dyDescent="0.2">
@@ -14917,38 +15047,38 @@
       <c r="C10" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="251" t="s">
+      <c r="D10" s="252" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="252"/>
-      <c r="F10" s="253"/>
-      <c r="G10" s="159" t="s">
+      <c r="E10" s="227"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="160" t="s">
+      <c r="H10" s="159" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="160" t="s">
+      <c r="I10" s="159" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="161" t="s">
+      <c r="J10" s="160" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="254" t="s">
+      <c r="K10" s="244" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="255"/>
-      <c r="M10" s="256"/>
-      <c r="N10" s="171" t="s">
+      <c r="L10" s="245"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="168" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="172" t="s">
+      <c r="O10" s="169" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="172" t="s">
+      <c r="P10" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="Q10" s="173" t="s">
+      <c r="Q10" s="170" t="s">
         <v>89</v>
       </c>
       <c r="R10" s="107"/>
@@ -14957,47 +15087,47 @@
     <row r="11" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B11" s="112"/>
       <c r="C11" s="113"/>
-      <c r="D11" s="257" t="s">
+      <c r="D11" s="229" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="258"/>
-      <c r="F11" s="259"/>
+      <c r="E11" s="230"/>
+      <c r="F11" s="231"/>
       <c r="G11" s="125">
         <f>Flujos!G4</f>
-        <v>179498</v>
+        <v>339674.47768000001</v>
       </c>
       <c r="H11" s="125">
         <f>G11/0.915</f>
-        <v>196172.6775956284</v>
-      </c>
-      <c r="I11" s="136">
+        <v>371228.93735519127</v>
+      </c>
+      <c r="I11" s="135">
         <f>Flujos!H4</f>
-        <v>0.65689928816999998</v>
+        <v>0.65746340794999991</v>
       </c>
       <c r="J11" s="125">
         <f>+I11*G11</f>
-        <v>117912.10842793866</v>
-      </c>
-      <c r="K11" s="265" t="s">
+        <v>223323.53968912899</v>
+      </c>
+      <c r="K11" s="223" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="266"/>
-      <c r="M11" s="267"/>
+      <c r="L11" s="224"/>
+      <c r="M11" s="225"/>
       <c r="N11" s="125">
         <f>Flujos!G12</f>
-        <v>179324</v>
+        <v>334236.40255</v>
       </c>
       <c r="O11" s="125">
         <f>N11/0.915</f>
-        <v>195982.51366120219</v>
-      </c>
-      <c r="P11" s="130">
+        <v>365285.68584699451</v>
+      </c>
+      <c r="P11" s="129">
         <f>Flujos!H12</f>
-        <v>0.65689999999999993</v>
-      </c>
-      <c r="Q11" s="170">
+        <v>0.65749999999999997</v>
+      </c>
+      <c r="Q11" s="167">
         <f>+P11*N11</f>
-        <v>117797.93559999998</v>
+        <v>219760.43467662498</v>
       </c>
       <c r="R11" s="107"/>
       <c r="T11" s="124"/>
@@ -15005,101 +15135,107 @@
     <row r="12" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="112"/>
       <c r="C12" s="113"/>
-      <c r="D12" s="257" t="s">
+      <c r="D12" s="229" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="258"/>
-      <c r="F12" s="259"/>
+      <c r="E12" s="230"/>
+      <c r="F12" s="231"/>
       <c r="G12" s="125">
         <f>Flujos!G6</f>
-        <v>181230</v>
+        <v>335900.43236999999</v>
       </c>
       <c r="H12" s="125">
         <f>G12/0.915</f>
-        <v>198065.57377049178</v>
-      </c>
-      <c r="I12" s="136">
+        <v>367104.2976721311</v>
+      </c>
+      <c r="I12" s="135">
         <f>Flujos!H6</f>
-        <v>0.65688254678999991</v>
+        <v>0.65748858436999991</v>
       </c>
       <c r="J12" s="125">
         <f>+I12*G12</f>
-        <v>119046.82395475169</v>
-      </c>
-      <c r="K12" s="265" t="s">
+        <v>220850.6997682222</v>
+      </c>
+      <c r="K12" s="223" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="266"/>
-      <c r="M12" s="267"/>
-      <c r="N12" s="125"/>
+      <c r="L12" s="224"/>
+      <c r="M12" s="225"/>
+      <c r="N12" s="125">
+        <f>'Datos Extra'!B6</f>
+        <v>51054</v>
+      </c>
       <c r="O12" s="125">
         <f>N12/0.915</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="170">
+        <v>55796.721311475405</v>
+      </c>
+      <c r="P12" s="129">
+        <f>Flujos!H31</f>
+        <v>0.65727023161999998</v>
+      </c>
+      <c r="Q12" s="167">
         <f>+P12*N12</f>
-        <v>0</v>
+        <v>33556.274405127479</v>
       </c>
       <c r="R12" s="107"/>
     </row>
     <row r="13" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="112"/>
       <c r="C13" s="113"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="253"/>
-      <c r="G13" s="278"/>
-      <c r="H13" s="279"/>
-      <c r="I13" s="279"/>
-      <c r="J13" s="280"/>
-      <c r="K13" s="268" t="s">
+      <c r="D13" s="252"/>
+      <c r="E13" s="227"/>
+      <c r="F13" s="228"/>
+      <c r="G13" s="220"/>
+      <c r="H13" s="221"/>
+      <c r="I13" s="221"/>
+      <c r="J13" s="222"/>
+      <c r="K13" s="232" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="269"/>
-      <c r="M13" s="270"/>
-      <c r="N13" s="134">
+      <c r="L13" s="233"/>
+      <c r="M13" s="234"/>
+      <c r="N13" s="133">
         <f>+SUM(N9:N12)</f>
-        <v>179324</v>
-      </c>
-      <c r="O13" s="134">
+        <v>385290.40255</v>
+      </c>
+      <c r="O13" s="133">
         <f>+SUM(O9:O12)</f>
-        <v>195982.51366120219</v>
-      </c>
-      <c r="P13" s="134"/>
-      <c r="Q13" s="135">
+        <v>421082.4071584699</v>
+      </c>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="134">
         <f>+SUM(Q9:Q12)</f>
-        <v>117797.93559999998</v>
+        <v>253316.70908175246</v>
       </c>
       <c r="R13" s="107"/>
     </row>
     <row r="14" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="112"/>
       <c r="C14" s="113"/>
-      <c r="D14" s="251" t="s">
+      <c r="D14" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="252"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="159" t="s">
+      <c r="E14" s="227"/>
+      <c r="F14" s="228"/>
+      <c r="G14" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="160" t="s">
+      <c r="H14" s="159" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="160" t="s">
+      <c r="I14" s="159" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="161" t="s">
+      <c r="J14" s="160" t="s">
         <v>89</v>
       </c>
-      <c r="K14" s="271"/>
-      <c r="L14" s="272"/>
-      <c r="M14" s="272"/>
-      <c r="N14" s="272"/>
-      <c r="O14" s="272"/>
-      <c r="P14" s="272"/>
-      <c r="Q14" s="273"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="254"/>
+      <c r="M14" s="254"/>
+      <c r="N14" s="254"/>
+      <c r="O14" s="254"/>
+      <c r="P14" s="254"/>
+      <c r="Q14" s="255"/>
       <c r="R14" s="107"/>
     </row>
     <row r="15" spans="2:20" ht="14" x14ac:dyDescent="0.2">
@@ -15112,35 +15248,35 @@
       <c r="F15" s="122"/>
       <c r="G15" s="125">
         <f>Flujos!G17</f>
-        <v>49366</v>
+        <v>49365.992154</v>
       </c>
       <c r="H15" s="125">
         <f>G15/0.915</f>
-        <v>53951.912568306012</v>
-      </c>
-      <c r="I15" s="136">
+        <v>53951.903993442618</v>
+      </c>
+      <c r="I15" s="135">
         <f>Flujos!H17</f>
-        <v>0.66156524052999999</v>
-      </c>
-      <c r="J15" s="179">
+        <v>0.66157444671999999</v>
+      </c>
+      <c r="J15" s="176">
         <f>+I15*G15</f>
-        <v>32658.829664003981</v>
-      </c>
-      <c r="K15" s="281" t="s">
+        <v>32659.27894606641</v>
+      </c>
+      <c r="K15" s="226" t="s">
         <v>103</v>
       </c>
-      <c r="L15" s="252"/>
-      <c r="M15" s="253"/>
-      <c r="N15" s="159" t="s">
+      <c r="L15" s="227"/>
+      <c r="M15" s="228"/>
+      <c r="N15" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="O15" s="160" t="s">
+      <c r="O15" s="159" t="s">
         <v>100</v>
       </c>
-      <c r="P15" s="160" t="s">
+      <c r="P15" s="159" t="s">
         <v>88</v>
       </c>
-      <c r="Q15" s="178" t="s">
+      <c r="Q15" s="175" t="s">
         <v>89</v>
       </c>
       <c r="R15" s="107"/>
@@ -15161,61 +15297,67 @@
         <f>G16/0.915</f>
         <v>56665.573770491799</v>
       </c>
-      <c r="I16" s="136">
+      <c r="I16" s="135">
         <f>Flujos!H19</f>
-        <v>0.66137186345999988</v>
+        <v>0.66137904486999999</v>
       </c>
       <c r="J16" s="125">
         <f>+I16*G16</f>
-        <v>34291.469748537536</v>
-      </c>
-      <c r="K16" s="260" t="s">
+        <v>34291.842097464629</v>
+      </c>
+      <c r="K16" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="L16" s="261"/>
-      <c r="M16" s="262"/>
-      <c r="N16" s="165">
+      <c r="L16" s="248"/>
+      <c r="M16" s="249"/>
+      <c r="N16" s="164">
         <f>Flujos!G27</f>
-        <v>61395</v>
+        <v>61528.683658000002</v>
       </c>
       <c r="O16" s="125">
         <f>N16/0.915</f>
-        <v>67098.360655737706</v>
-      </c>
-      <c r="P16" s="166">
+        <v>67244.463014207649</v>
+      </c>
+      <c r="P16" s="165">
         <f>Flujos!H27</f>
         <v>0.66079999999999994</v>
       </c>
-      <c r="Q16" s="177">
+      <c r="Q16" s="174">
         <f>+P16*N16</f>
-        <v>40569.815999999999</v>
+        <v>40658.154161206396</v>
       </c>
       <c r="R16" s="107"/>
     </row>
     <row r="17" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="112"/>
       <c r="C17" s="113"/>
-      <c r="D17" s="257"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="259"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="230"/>
+      <c r="F17" s="231"/>
       <c r="G17" s="125"/>
       <c r="H17" s="125"/>
-      <c r="I17" s="133"/>
+      <c r="I17" s="132"/>
       <c r="J17" s="125"/>
-      <c r="K17" s="127" t="s">
+      <c r="K17" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="L17" s="128"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="131"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="130">
+        <f>'Datos Extra'!B7</f>
+        <v>46714.41</v>
+      </c>
       <c r="O17" s="125">
         <f>N17/0.915</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="170">
+        <v>51054</v>
+      </c>
+      <c r="P17" s="131">
+        <f>Flujos!H31</f>
+        <v>0.65727023161999998</v>
+      </c>
+      <c r="Q17" s="167">
         <f>+P17*N17</f>
-        <v>0</v>
+        <v>30703.991080691645</v>
       </c>
       <c r="R17" s="107"/>
     </row>
@@ -15224,448 +15366,490 @@
       <c r="C18" s="113" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="263" t="s">
+      <c r="D18" s="250" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="134">
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="133">
         <f>+SUM(G10:G17)</f>
-        <v>461943</v>
-      </c>
-      <c r="H18" s="134">
+        <v>776789.90220400004</v>
+      </c>
+      <c r="H18" s="133">
         <f>+SUM(H10:H17)</f>
-        <v>504855.73770491802</v>
-      </c>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134">
+        <v>848950.71279125672</v>
+      </c>
+      <c r="I18" s="133"/>
+      <c r="J18" s="133">
         <f>+SUM(J10:J17)</f>
-        <v>303909.23179523187</v>
-      </c>
-      <c r="K18" s="162" t="s">
+        <v>511125.36050088215</v>
+      </c>
+      <c r="K18" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="163"/>
-      <c r="M18" s="164"/>
-      <c r="N18" s="134">
+      <c r="L18" s="162"/>
+      <c r="M18" s="163"/>
+      <c r="N18" s="133">
         <f>+SUM(N14:N17)</f>
-        <v>61395</v>
-      </c>
-      <c r="O18" s="134">
+        <v>108243.093658</v>
+      </c>
+      <c r="O18" s="133">
         <f>+SUM(O14:O17)</f>
-        <v>67098.360655737706</v>
-      </c>
-      <c r="P18" s="134"/>
-      <c r="Q18" s="135">
+        <v>118298.46301420765</v>
+      </c>
+      <c r="P18" s="133"/>
+      <c r="Q18" s="134">
         <f>+SUM(Q14:Q17)</f>
-        <v>40569.815999999999</v>
+        <v>71362.145241898048</v>
       </c>
       <c r="R18" s="107"/>
-      <c r="S18" s="137"/>
-      <c r="T18" s="138"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="137"/>
     </row>
     <row r="19" spans="2:21" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="112"/>
       <c r="C19" s="113"/>
-      <c r="D19" s="248" t="s">
+      <c r="D19" s="238" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="249"/>
-      <c r="I19" s="249"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="287"/>
-      <c r="M19" s="288"/>
+      <c r="E19" s="239"/>
+      <c r="F19" s="239"/>
+      <c r="G19" s="239"/>
+      <c r="H19" s="239"/>
+      <c r="I19" s="239"/>
+      <c r="J19" s="240"/>
+      <c r="K19" s="241"/>
+      <c r="L19" s="242"/>
+      <c r="M19" s="243"/>
       <c r="N19" s="118"/>
       <c r="O19" s="118"/>
       <c r="P19" s="118"/>
       <c r="Q19" s="119"/>
       <c r="R19" s="107"/>
-      <c r="S19" s="139"/>
+      <c r="S19" s="138"/>
     </row>
     <row r="20" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="112"/>
       <c r="C20" s="113"/>
-      <c r="D20" s="254" t="s">
+      <c r="D20" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="255"/>
-      <c r="F20" s="256"/>
-      <c r="G20" s="171" t="s">
+      <c r="E20" s="245"/>
+      <c r="F20" s="246"/>
+      <c r="G20" s="168" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="172" t="s">
+      <c r="H20" s="169" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="172" t="s">
+      <c r="I20" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="173" t="s">
+      <c r="J20" s="170" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="254" t="s">
-        <v>101</v>
-      </c>
-      <c r="L20" s="255"/>
-      <c r="M20" s="256"/>
-      <c r="N20" s="167" t="s">
+      <c r="K20" s="244" t="s">
+        <v>117</v>
+      </c>
+      <c r="L20" s="245"/>
+      <c r="M20" s="246"/>
+      <c r="N20" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="O20" s="168" t="s">
+      <c r="O20" s="287" t="s">
         <v>100</v>
       </c>
-      <c r="P20" s="168" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q20" s="169" t="s">
-        <v>89</v>
-      </c>
+      <c r="P20" s="156"/>
+      <c r="Q20" s="156"/>
       <c r="R20" s="107"/>
-      <c r="S20" s="140"/>
+      <c r="S20" s="139"/>
     </row>
     <row r="21" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="112"/>
       <c r="C21" s="113"/>
-      <c r="D21" s="257" t="s">
+      <c r="D21" s="229" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="258"/>
-      <c r="F21" s="259"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="170">
+      <c r="E21" s="230"/>
+      <c r="F21" s="231"/>
+      <c r="G21" s="125">
+        <f>'Datos Extra'!B2</f>
+        <v>289626.78000000003</v>
+      </c>
+      <c r="H21" s="125">
+        <f>G21/0.915</f>
+        <v>316532</v>
+      </c>
+      <c r="I21" s="135">
+        <f>'Datos Extra'!C2</f>
+        <v>0.65752410482089585</v>
+      </c>
+      <c r="J21" s="167">
         <f>+I21*G21</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="260" t="s">
+        <v>190436.58925165856</v>
+      </c>
+      <c r="K21" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="L21" s="261"/>
-      <c r="M21" s="262"/>
-      <c r="N21" s="123"/>
+      <c r="L21" s="248"/>
+      <c r="M21" s="249"/>
+      <c r="N21" s="123">
+        <f>'Datos Extra'!B4</f>
+        <v>50953.72980833333</v>
+      </c>
       <c r="O21" s="125">
         <f>N21/0.915</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="170"/>
+        <v>55687.136402550088</v>
+      </c>
+      <c r="P21" s="285"/>
+      <c r="Q21" s="124"/>
       <c r="R21" s="107"/>
-      <c r="S21" s="140"/>
+      <c r="S21" s="139"/>
     </row>
     <row r="22" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="112"/>
       <c r="C22" s="113"/>
-      <c r="D22" s="257" t="s">
+      <c r="D22" s="229" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="258"/>
-      <c r="F22" s="259"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="170">
+      <c r="E22" s="230"/>
+      <c r="F22" s="231"/>
+      <c r="G22" s="125">
+        <f>'Datos Extra'!B3</f>
+        <v>229007.11500000002</v>
+      </c>
+      <c r="H22" s="125">
+        <f>G22/0.915</f>
+        <v>250281</v>
+      </c>
+      <c r="I22" s="135">
+        <f>'Datos Extra'!C3</f>
+        <v>0.657301820571914</v>
+      </c>
+      <c r="J22" s="167">
         <f>+I22*G22</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="127" t="s">
+        <v>150526.7936134217</v>
+      </c>
+      <c r="K22" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="L22" s="128"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="123"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="128"/>
+      <c r="N22" s="123">
+        <f>'Datos Extra'!B5</f>
+        <v>233375.03383500004</v>
+      </c>
       <c r="O22" s="125">
         <f>N22/0.915</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="170"/>
+        <v>255054.68178688528</v>
+      </c>
+      <c r="P22" s="285"/>
+      <c r="Q22" s="124"/>
       <c r="R22" s="107"/>
-      <c r="S22" s="140"/>
+      <c r="S22" s="139"/>
     </row>
     <row r="23" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="112"/>
       <c r="C23" s="113"/>
-      <c r="D23" s="268" t="s">
+      <c r="D23" s="232" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="269"/>
-      <c r="F23" s="270"/>
-      <c r="G23" s="134">
+      <c r="E23" s="233"/>
+      <c r="F23" s="234"/>
+      <c r="G23" s="133">
         <f>+SUM(G19:G22)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="134">
+        <v>518633.89500000002</v>
+      </c>
+      <c r="H23" s="133">
         <f>+SUM(H19:H22)</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="135">
+        <v>566813</v>
+      </c>
+      <c r="I23" s="140"/>
+      <c r="J23" s="134">
         <f>+SUM(J21:J22)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="127" t="s">
+        <v>340963.38286508026</v>
+      </c>
+      <c r="K23" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="L23" s="128"/>
-      <c r="M23" s="129"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="128"/>
       <c r="N23" s="123"/>
       <c r="O23" s="123"/>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="170"/>
+      <c r="P23" s="285"/>
+      <c r="Q23" s="124"/>
       <c r="R23" s="107"/>
-      <c r="S23" s="139"/>
-    </row>
-    <row r="24" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="S23" s="138"/>
+    </row>
+    <row r="24" spans="2:21" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="112"/>
       <c r="C24" s="113"/>
-      <c r="D24" s="282" t="s">
+      <c r="D24" s="235" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="283"/>
-      <c r="F24" s="284"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="176">
+      <c r="E24" s="236"/>
+      <c r="F24" s="237"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="171"/>
+      <c r="I24" s="172"/>
+      <c r="J24" s="173">
         <f>+I24*G24</f>
         <v>0</v>
       </c>
-      <c r="K24" s="274"/>
-      <c r="L24" s="275"/>
-      <c r="M24" s="275"/>
-      <c r="N24" s="275"/>
-      <c r="O24" s="275"/>
-      <c r="P24" s="275"/>
-      <c r="Q24" s="276"/>
+      <c r="K24" s="217"/>
+      <c r="L24" s="218"/>
+      <c r="M24" s="218"/>
+      <c r="N24" s="218"/>
+      <c r="O24" s="288"/>
+      <c r="P24" s="286"/>
+      <c r="Q24" s="286"/>
       <c r="R24" s="107"/>
     </row>
     <row r="25" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B25" s="112"/>
       <c r="C25" s="113"/>
-      <c r="I25" s="145"/>
-      <c r="J25" s="145"/>
+      <c r="I25" s="144"/>
+      <c r="J25" s="144"/>
       <c r="R25" s="107"/>
-      <c r="S25" s="140"/>
+      <c r="S25" s="139"/>
     </row>
     <row r="26" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="112"/>
       <c r="C26" s="113"/>
-      <c r="I26" s="145"/>
-      <c r="J26" s="145"/>
-      <c r="N26" s="145"/>
-      <c r="O26" s="145"/>
-      <c r="R26" s="142"/>
+      <c r="I26" s="144"/>
+      <c r="J26" s="144"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="144"/>
+      <c r="R26" s="141"/>
     </row>
     <row r="27" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B27" s="112"/>
       <c r="C27" s="113"/>
-      <c r="I27" s="145" t="s">
+      <c r="I27" s="144" t="s">
         <v>93</v>
       </c>
-      <c r="J27" s="145" t="s">
+      <c r="J27" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="N27" s="145"/>
-      <c r="O27" s="145"/>
-      <c r="P27" s="143"/>
-      <c r="Q27" s="143"/>
+      <c r="N27" s="144"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="142"/>
+      <c r="Q27" s="142"/>
       <c r="R27" s="107"/>
-      <c r="U27" s="144"/>
+      <c r="U27" s="143"/>
     </row>
     <row r="28" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="112"/>
       <c r="C28" s="113"/>
-      <c r="I28" s="145">
+      <c r="I28" s="144">
         <f>[1]Flujos!G9</f>
         <v>-19721</v>
       </c>
-      <c r="J28" s="145">
+      <c r="J28" s="144">
         <f>'[1]Mapa de Procesos'!L118</f>
         <v>-8270.0017400813813</v>
       </c>
-      <c r="N28" s="145"/>
-      <c r="O28" s="145"/>
-      <c r="P28" s="143"/>
-      <c r="Q28" s="143"/>
-      <c r="R28" s="142"/>
-      <c r="U28" s="144"/>
+      <c r="N28" s="144"/>
+      <c r="O28" s="144"/>
+      <c r="P28" s="142"/>
+      <c r="Q28" s="142"/>
+      <c r="R28" s="141"/>
+      <c r="U28" s="143"/>
     </row>
     <row r="29" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B29" s="112"/>
       <c r="C29" s="113"/>
-      <c r="I29" s="145">
+      <c r="I29" s="144">
         <f>[1]Flujos!G17</f>
         <v>-2071</v>
       </c>
-      <c r="J29" s="145">
+      <c r="J29" s="144">
         <f>'[1]Mapa de Procesos'!L119</f>
         <v>-852.7457844552099</v>
       </c>
-      <c r="N29" s="145"/>
-      <c r="O29" s="145"/>
-      <c r="P29" s="143" t="s">
+      <c r="N29" s="144"/>
+      <c r="O29" s="144"/>
+      <c r="P29" s="142" t="s">
         <v>95</v>
       </c>
-      <c r="Q29" s="143"/>
+      <c r="Q29" s="142"/>
       <c r="R29" s="107"/>
-      <c r="U29" s="144"/>
+      <c r="U29" s="143"/>
     </row>
     <row r="30" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B30" s="112"/>
       <c r="C30" s="113"/>
-      <c r="I30" s="145">
+      <c r="I30" s="144">
         <f>[1]Flujos!G21</f>
         <v>51</v>
       </c>
-      <c r="J30" s="145">
+      <c r="J30" s="144">
         <f>'[1]Mapa de Procesos'!L121</f>
         <v>34.489375057529998</v>
       </c>
-      <c r="N30" s="145"/>
-      <c r="O30" s="145"/>
-      <c r="P30" s="146"/>
-      <c r="Q30" s="143"/>
+      <c r="N30" s="144"/>
+      <c r="O30" s="144"/>
+      <c r="P30" s="145"/>
+      <c r="Q30" s="142"/>
       <c r="R30" s="107"/>
-      <c r="U30" s="144"/>
+      <c r="U30" s="143"/>
     </row>
     <row r="31" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B31" s="112"/>
       <c r="C31" s="113"/>
-      <c r="I31" s="145">
+      <c r="I31" s="144">
         <f>[1]Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="J31" s="145">
+      <c r="J31" s="144">
         <f>'[1]Mapa de Procesos'!L122</f>
         <v>0</v>
       </c>
-      <c r="N31" s="145"/>
-      <c r="O31" s="145"/>
-      <c r="P31" s="146"/>
-      <c r="Q31" s="143"/>
-      <c r="R31" s="142"/>
-      <c r="U31" s="144"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="145"/>
+      <c r="Q31" s="142"/>
+      <c r="R31" s="141"/>
+      <c r="U31" s="143"/>
     </row>
     <row r="32" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B32" s="112"/>
       <c r="C32" s="113"/>
-      <c r="I32" s="145">
+      <c r="I32" s="144">
         <f>[1]Flujos!G26</f>
         <v>-21285</v>
       </c>
-      <c r="J32" s="145">
+      <c r="J32" s="144">
         <f>'[1]Mapa de Procesos'!L128</f>
         <v>-13448.820825000001</v>
       </c>
-      <c r="N32" s="145"/>
-      <c r="O32" s="145"/>
-      <c r="P32" s="143"/>
-      <c r="Q32" s="143"/>
+      <c r="N32" s="144"/>
+      <c r="O32" s="144"/>
+      <c r="P32" s="142"/>
+      <c r="Q32" s="142"/>
       <c r="R32" s="107"/>
-      <c r="U32" s="144"/>
+      <c r="U32" s="143"/>
     </row>
     <row r="33" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B33" s="112"/>
       <c r="C33" s="113"/>
-      <c r="I33" s="145">
+      <c r="I33" s="144">
         <f>[1]Flujos!G34</f>
         <v>-63213</v>
       </c>
-      <c r="J33" s="145">
+      <c r="J33" s="144">
         <f>'[1]Mapa de Procesos'!L129</f>
         <v>-38546.283837997558</v>
       </c>
-      <c r="N33" s="145"/>
-      <c r="O33" s="145"/>
-      <c r="P33" s="147"/>
-      <c r="Q33" s="148"/>
-      <c r="R33" s="142"/>
-      <c r="U33" s="144"/>
+      <c r="N33" s="144"/>
+      <c r="O33" s="144"/>
+      <c r="P33" s="146"/>
+      <c r="Q33" s="147"/>
+      <c r="R33" s="141"/>
+      <c r="U33" s="143"/>
     </row>
     <row r="34" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B34" s="112"/>
       <c r="C34" s="113"/>
-      <c r="I34" s="145">
+      <c r="I34" s="144">
         <f>[1]Flujos!G39</f>
         <v>1032</v>
       </c>
-      <c r="J34" s="145">
+      <c r="J34" s="144">
         <f>'[1]Mapa de Procesos'!L130</f>
         <v>613.62720000000002</v>
       </c>
-      <c r="N34" s="145"/>
-      <c r="O34" s="145"/>
-      <c r="P34" s="148"/>
-      <c r="Q34" s="148"/>
+      <c r="N34" s="144"/>
+      <c r="O34" s="144"/>
+      <c r="P34" s="147"/>
+      <c r="Q34" s="147"/>
       <c r="R34" s="107"/>
-      <c r="U34" s="144"/>
+      <c r="U34" s="143"/>
     </row>
     <row r="35" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="149"/>
-      <c r="C35" s="150"/>
-      <c r="D35" s="150"/>
-      <c r="E35" s="150"/>
-      <c r="F35" s="150"/>
-      <c r="G35" s="150"/>
-      <c r="H35" s="150"/>
-      <c r="I35" s="151">
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="149"/>
+      <c r="G35" s="149"/>
+      <c r="H35" s="149"/>
+      <c r="I35" s="150">
         <f>SUM(I28:I34)</f>
         <v>-105207</v>
       </c>
-      <c r="J35" s="151">
+      <c r="J35" s="150">
         <f>SUM(J28:J34)</f>
         <v>-60469.735612476616</v>
       </c>
-      <c r="K35" s="150"/>
-      <c r="L35" s="150"/>
-      <c r="M35" s="150"/>
-      <c r="N35" s="150"/>
-      <c r="O35" s="150"/>
-      <c r="P35" s="150"/>
-      <c r="Q35" s="150"/>
-      <c r="R35" s="152"/>
+      <c r="K35" s="149"/>
+      <c r="L35" s="149"/>
+      <c r="M35" s="149"/>
+      <c r="N35" s="149"/>
+      <c r="O35" s="149"/>
+      <c r="P35" s="149"/>
+      <c r="Q35" s="149"/>
+      <c r="R35" s="151"/>
     </row>
     <row r="38" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E38" s="153"/>
-      <c r="F38" s="153"/>
-      <c r="G38" s="153"/>
-      <c r="H38" s="153"/>
-      <c r="I38" s="154"/>
-      <c r="J38" s="154"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="152"/>
+      <c r="H38" s="152"/>
+      <c r="I38" s="153"/>
+      <c r="J38" s="153"/>
     </row>
     <row r="39" spans="2:21" ht="14" x14ac:dyDescent="0.2">
-      <c r="E39" s="153"/>
-      <c r="F39" s="153"/>
-      <c r="G39" s="153"/>
-      <c r="H39" s="153"/>
-      <c r="I39" s="154"/>
-      <c r="J39" s="154"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="153"/>
+      <c r="J39" s="153"/>
     </row>
     <row r="40" spans="2:21" ht="14" x14ac:dyDescent="0.2">
-      <c r="E40" s="155"/>
-      <c r="F40" s="155"/>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="155"/>
-      <c r="J40" s="155"/>
-      <c r="K40" s="155"/>
+      <c r="E40" s="154"/>
+      <c r="F40" s="154"/>
+      <c r="G40" s="154"/>
+      <c r="H40" s="154"/>
+      <c r="I40" s="154"/>
+      <c r="J40" s="154"/>
+      <c r="K40" s="154"/>
     </row>
     <row r="41" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E41" s="277"/>
-      <c r="F41" s="277"/>
-      <c r="G41" s="277"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="157"/>
-      <c r="J41" s="158"/>
+      <c r="E41" s="219"/>
+      <c r="F41" s="219"/>
+      <c r="G41" s="219"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="156"/>
+      <c r="J41" s="157"/>
       <c r="K41" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K24:O24"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="K7:M8"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="D2:E5"/>
+    <mergeCell ref="F2:Q3"/>
+    <mergeCell ref="F4:L5"/>
+    <mergeCell ref="M4:N5"/>
+    <mergeCell ref="P4:Q5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="K14:Q14"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="K11:M11"/>
@@ -15681,28 +15865,6 @@
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="K14:Q14"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="K7:M8"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="D2:E5"/>
-    <mergeCell ref="F2:Q3"/>
-    <mergeCell ref="F4:L5"/>
-    <mergeCell ref="M4:N5"/>
-    <mergeCell ref="P4:Q5"/>
-    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="45" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
